--- a/Channel_List/ABC_channel_list_LEAP.xlsx
+++ b/Channel_List/ABC_channel_list_LEAP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pkbu004\Downloads\RENEWXfer\Channel_List\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2194115072841/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B97223-C841-4E79-B14E-A89BF28A6871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{06B97223-C841-4E79-B14E-A89BF28A6871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD1913D2-EAFF-4CB0-B482-A9D68E4AC58A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="25980" yWindow="0" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Channel_Tags" sheetId="3" r:id="rId1"/>
@@ -2869,24 +2869,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73A017B1-6AB4-4932-A88F-508022D5A5BC}">
   <dimension ref="A1:BO1820"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="43.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="44.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="46.54296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="37" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="29.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="19" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="49.21875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="53.44140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="43.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="49.109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="48.77734375" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="38.44140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="32" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="33.21875" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="29" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="40.77734375" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="41" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="33.5546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="40.44140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="40" bestFit="1" customWidth="1"/>
+    <col min="65" max="67" width="33.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:67" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3089,7 +3132,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:67" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -3286,7 +3329,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
         <v>154</v>
       </c>
@@ -3471,7 +3514,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>215</v>
       </c>
@@ -3656,7 +3699,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>276</v>
       </c>
@@ -3841,7 +3884,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="6" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>337</v>
       </c>
@@ -4026,7 +4069,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="7" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>398</v>
       </c>
@@ -4211,7 +4254,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="8" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>459</v>
       </c>
@@ -4396,7 +4439,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="9" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>520</v>
       </c>
@@ -4581,7 +4624,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>581</v>
       </c>
@@ -4766,10 +4809,10 @@
         <v>641</v>
       </c>
     </row>
-    <row r="1482" spans="7:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="1482" spans="7:7" ht="15" x14ac:dyDescent="0.3">
       <c r="G1482" s="3"/>
     </row>
-    <row r="1820" spans="7:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="1820" spans="7:7" ht="15" x14ac:dyDescent="0.3">
       <c r="G1820" s="3"/>
     </row>
   </sheetData>
@@ -4781,15 +4824,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399253C3-383B-4F1D-9B29-066F91863EF5}">
   <dimension ref="A1:D1775"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -4803,7 +4846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4817,5380 +4860,5380 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C3" s="4"/>
       <c r="D3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4" s="4"/>
       <c r="D4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5" s="4"/>
       <c r="D5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C6" s="4"/>
       <c r="D6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C7" s="4"/>
       <c r="D7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C8" s="4"/>
       <c r="D8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C9" s="4"/>
       <c r="D9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C10" s="4"/>
       <c r="D10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C11" s="4"/>
       <c r="D11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C12" s="4"/>
       <c r="D12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C13" s="4"/>
       <c r="D13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C14" s="4"/>
       <c r="D14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C15" s="4"/>
       <c r="D15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C16" s="4"/>
       <c r="D16" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" s="4"/>
       <c r="D17" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" s="4"/>
       <c r="D18" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" s="4"/>
       <c r="D19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" s="4"/>
       <c r="D20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C21" s="4"/>
       <c r="D21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C22" s="4"/>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C23" s="4"/>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C24" s="4"/>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C25" s="4"/>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C26" s="4"/>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C27" s="4"/>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C28" s="4"/>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C29" s="4"/>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C30" s="4"/>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C31" s="4"/>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C32" s="4"/>
     </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" s="4"/>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" s="4"/>
     </row>
-    <row r="35" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" s="4"/>
     </row>
-    <row r="36" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" s="4"/>
     </row>
-    <row r="37" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" s="4"/>
     </row>
-    <row r="38" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" s="4"/>
     </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" s="4"/>
     </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" s="4"/>
     </row>
-    <row r="41" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" s="4"/>
     </row>
-    <row r="42" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" s="4"/>
     </row>
-    <row r="43" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" s="4"/>
     </row>
-    <row r="44" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" s="4"/>
     </row>
-    <row r="45" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" s="4"/>
     </row>
-    <row r="46" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" s="4"/>
     </row>
-    <row r="47" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" s="4"/>
     </row>
-    <row r="48" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C48" s="4"/>
     </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" s="4"/>
     </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" s="4"/>
     </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" s="4"/>
     </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" s="4"/>
     </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" s="4"/>
     </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" s="4"/>
     </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" s="4"/>
     </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" s="4"/>
     </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" s="4"/>
     </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" s="4"/>
     </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" s="4"/>
     </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" s="4"/>
     </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" s="4"/>
     </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" s="4"/>
     </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" s="4"/>
     </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" s="4"/>
     </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" s="4"/>
     </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" s="4"/>
     </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" s="4"/>
     </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" s="4"/>
     </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" s="4"/>
     </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" s="4"/>
     </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="4"/>
     </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" s="4"/>
     </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" s="4"/>
     </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" s="4"/>
     </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" s="4"/>
     </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" s="4"/>
     </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" s="4"/>
     </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" s="4"/>
     </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" s="4"/>
     </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" s="4"/>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" s="4"/>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C82" s="4"/>
     </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" s="4"/>
     </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C84" s="4"/>
     </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C85" s="4"/>
     </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C86" s="4"/>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C87" s="4"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C88" s="4"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C89" s="4"/>
     </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="90" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C90" s="4"/>
     </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="91" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C91" s="4"/>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C92" s="4"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C93" s="4"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C94" s="4"/>
     </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="95" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C95" s="4"/>
     </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="96" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C96" s="4"/>
     </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C97" s="4"/>
     </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="98" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C98" s="4"/>
     </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C99" s="4"/>
     </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C100" s="4"/>
     </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C101" s="4"/>
     </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="102" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C102" s="4"/>
     </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="103" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C103" s="4"/>
     </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="104" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C104" s="4"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C105" s="4"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C106" s="4"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C107" s="4"/>
     </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="108" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C108" s="4"/>
     </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="109" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C109" s="4"/>
     </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="110" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C110" s="4"/>
     </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="111" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C111" s="4"/>
     </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="112" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C112" s="4"/>
     </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C113" s="4"/>
     </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="114" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C114" s="4"/>
     </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="115" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C115" s="4"/>
     </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="116" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C116" s="4"/>
     </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="117" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C117" s="4"/>
     </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="118" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C118" s="4"/>
     </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="119" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C119" s="4"/>
     </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="120" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C120" s="4"/>
     </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="121" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C121" s="4"/>
     </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="122" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C122" s="4"/>
     </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="123" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C123" s="4"/>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="124" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C124" s="4"/>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="125" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C125" s="4"/>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="126" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C126" s="4"/>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="127" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C127" s="4"/>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="128" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C128" s="4"/>
     </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C129" s="4"/>
     </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="130" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C130" s="4"/>
     </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="131" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C131" s="4"/>
     </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="132" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C132" s="4"/>
     </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="133" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C133" s="4"/>
     </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="134" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C134" s="4"/>
     </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="135" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C135" s="4"/>
     </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C136" s="4"/>
     </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C137" s="4"/>
     </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C138" s="4"/>
     </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="139" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C139" s="4"/>
     </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="140" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C140" s="4"/>
     </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="141" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C141" s="4"/>
     </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C142" s="4"/>
     </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="143" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C143" s="4"/>
     </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="144" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C144" s="4"/>
     </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="145" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C145" s="4"/>
     </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="146" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C146" s="4"/>
     </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="147" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C147" s="4"/>
     </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="148" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C148" s="4"/>
     </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="149" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C149" s="4"/>
     </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="150" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C150" s="4"/>
     </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="151" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C151" s="4"/>
     </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="152" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C152" s="4"/>
     </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="153" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C153" s="4"/>
     </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="154" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C154" s="4"/>
     </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="155" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C155" s="4"/>
     </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="156" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C156" s="4"/>
     </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="157" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C157" s="4"/>
     </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="158" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C158" s="4"/>
     </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="159" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C159" s="4"/>
     </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="160" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C160" s="4"/>
     </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="161" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C161" s="4"/>
     </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="162" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C162" s="4"/>
     </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="163" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C163" s="4"/>
     </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="164" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C164" s="4"/>
     </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="165" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C165" s="4"/>
     </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="166" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C166" s="4"/>
     </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="167" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C167" s="4"/>
     </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="168" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C168" s="4"/>
     </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="169" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C169" s="4"/>
     </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="170" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C170" s="4"/>
     </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="171" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C171" s="4"/>
     </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="172" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C172" s="4"/>
     </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="173" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C173" s="4"/>
     </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="174" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C174" s="4"/>
     </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="175" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C175" s="4"/>
     </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="176" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C176" s="4"/>
     </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="177" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C177" s="4"/>
     </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="178" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C178" s="4"/>
     </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="179" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C179" s="4"/>
     </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="180" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C180" s="4"/>
     </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="181" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C181" s="4"/>
     </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="182" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C182" s="4"/>
     </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="183" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C183" s="4"/>
     </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="184" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C184" s="4"/>
     </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="185" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C185" s="4"/>
     </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="186" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C186" s="4"/>
     </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="187" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C187" s="4"/>
     </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="188" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C188" s="4"/>
     </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="189" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C189" s="4"/>
     </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="190" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C190" s="4"/>
     </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="191" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C191" s="4"/>
     </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="192" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C192" s="4"/>
     </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="193" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C193" s="4"/>
     </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="194" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C194" s="4"/>
     </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="195" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C195" s="4"/>
     </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="196" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C196" s="4"/>
     </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="197" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C197" s="4"/>
     </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="198" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C198" s="4"/>
     </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="199" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C199" s="4"/>
     </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="200" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C200" s="4"/>
     </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="201" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C201" s="4"/>
     </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="202" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C202" s="4"/>
     </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="203" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C203" s="4"/>
     </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="204" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C204" s="4"/>
     </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="205" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C205" s="4"/>
     </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="206" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C206" s="4"/>
     </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="207" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C207" s="4"/>
     </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="208" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C208" s="4"/>
     </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="209" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C209" s="4"/>
     </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="210" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C210" s="4"/>
     </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="211" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C211" s="4"/>
     </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="212" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C212" s="4"/>
     </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="213" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C213" s="4"/>
     </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="214" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C214" s="4"/>
     </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="215" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C215" s="4"/>
     </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="216" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C216" s="4"/>
     </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="217" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C217" s="4"/>
     </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="218" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C218" s="4"/>
     </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="219" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C219" s="4"/>
     </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="220" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C220" s="4"/>
     </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="221" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C221" s="4"/>
     </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="222" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C222" s="4"/>
     </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="223" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C223" s="4"/>
     </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="224" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C224" s="4"/>
     </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="225" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C225" s="4"/>
     </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="226" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C226" s="4"/>
     </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="227" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C227" s="4"/>
     </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="228" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C228" s="4"/>
     </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="229" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C229" s="4"/>
     </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="230" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C230" s="4"/>
     </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="231" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C231" s="4"/>
     </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="232" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C232" s="4"/>
     </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="233" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C233" s="4"/>
     </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="234" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C234" s="4"/>
     </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="235" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C235" s="4"/>
     </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="236" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C236" s="4"/>
     </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="237" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C237" s="4"/>
     </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="238" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C238" s="4"/>
     </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="239" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C239" s="4"/>
     </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="240" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C240" s="4"/>
     </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="241" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C241" s="4"/>
     </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="242" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C242" s="4"/>
     </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="243" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C243" s="4"/>
     </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="244" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C244" s="4"/>
     </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="245" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C245" s="4"/>
     </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="246" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C246" s="4"/>
     </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="247" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C247" s="4"/>
     </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="248" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C248" s="4"/>
     </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="249" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C249" s="4"/>
     </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="250" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C250" s="4"/>
     </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="251" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C251" s="4"/>
     </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="252" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C252" s="4"/>
     </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="253" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C253" s="4"/>
     </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="254" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C254" s="4"/>
     </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="255" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C255" s="4"/>
     </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="256" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C256" s="4"/>
     </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="257" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C257" s="4"/>
     </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="258" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C258" s="4"/>
     </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="259" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C259" s="4"/>
     </row>
-    <row r="260" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="260" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C260" s="4"/>
     </row>
-    <row r="261" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="261" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C261" s="4"/>
     </row>
-    <row r="262" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="262" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C262" s="4"/>
     </row>
-    <row r="263" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="263" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C263" s="4"/>
     </row>
-    <row r="264" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="264" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C264" s="4"/>
     </row>
-    <row r="265" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="265" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C265" s="4"/>
     </row>
-    <row r="266" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="266" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C266" s="4"/>
     </row>
-    <row r="267" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="267" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C267" s="4"/>
     </row>
-    <row r="268" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="268" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C268" s="4"/>
     </row>
-    <row r="269" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="269" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C269" s="4"/>
     </row>
-    <row r="270" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="270" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C270" s="4"/>
     </row>
-    <row r="271" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="271" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C271" s="4"/>
     </row>
-    <row r="272" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="272" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C272" s="4"/>
     </row>
-    <row r="273" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="273" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C273" s="4"/>
     </row>
-    <row r="274" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="274" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C274" s="4"/>
     </row>
-    <row r="275" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="275" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C275" s="4"/>
     </row>
-    <row r="276" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="276" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C276" s="4"/>
     </row>
-    <row r="277" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="277" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C277" s="4"/>
     </row>
-    <row r="278" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="278" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C278" s="4"/>
     </row>
-    <row r="279" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="279" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C279" s="4"/>
     </row>
-    <row r="280" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="280" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C280" s="4"/>
     </row>
-    <row r="281" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="281" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C281" s="4"/>
     </row>
-    <row r="282" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="282" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C282" s="4"/>
     </row>
-    <row r="283" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="283" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C283" s="4"/>
     </row>
-    <row r="284" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="284" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C284" s="4"/>
     </row>
-    <row r="285" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="285" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C285" s="4"/>
     </row>
-    <row r="286" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="286" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C286" s="4"/>
     </row>
-    <row r="287" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="287" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C287" s="4"/>
     </row>
-    <row r="288" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="288" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C288" s="4"/>
     </row>
-    <row r="289" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="289" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C289" s="4"/>
     </row>
-    <row r="290" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="290" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C290" s="4"/>
     </row>
-    <row r="291" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="291" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C291" s="4"/>
     </row>
-    <row r="292" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="292" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C292" s="4"/>
     </row>
-    <row r="293" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="293" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C293" s="4"/>
     </row>
-    <row r="294" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="294" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C294" s="4"/>
     </row>
-    <row r="295" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="295" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C295" s="4"/>
     </row>
-    <row r="296" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="296" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C296" s="4"/>
     </row>
-    <row r="297" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="297" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C297" s="4"/>
     </row>
-    <row r="298" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="298" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C298" s="4"/>
     </row>
-    <row r="299" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="299" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C299" s="4"/>
     </row>
-    <row r="300" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="300" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C300" s="4"/>
     </row>
-    <row r="301" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="301" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C301" s="4"/>
     </row>
-    <row r="302" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="302" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C302" s="4"/>
     </row>
-    <row r="303" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="303" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C303" s="4"/>
     </row>
-    <row r="304" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="304" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C304" s="4"/>
     </row>
-    <row r="305" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="305" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C305" s="4"/>
     </row>
-    <row r="306" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="306" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C306" s="4"/>
     </row>
-    <row r="307" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="307" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C307" s="4"/>
     </row>
-    <row r="308" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="308" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C308" s="4"/>
     </row>
-    <row r="309" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="309" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C309" s="4"/>
     </row>
-    <row r="310" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="310" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C310" s="4"/>
     </row>
-    <row r="311" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="311" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C311" s="4"/>
     </row>
-    <row r="312" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="312" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C312" s="4"/>
     </row>
-    <row r="313" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="313" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C313" s="4"/>
     </row>
-    <row r="314" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="314" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C314" s="4"/>
     </row>
-    <row r="315" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="315" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C315" s="4"/>
     </row>
-    <row r="316" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="316" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C316" s="4"/>
     </row>
-    <row r="317" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="317" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C317" s="4"/>
     </row>
-    <row r="318" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="318" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C318" s="4"/>
     </row>
-    <row r="319" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="319" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C319" s="4"/>
     </row>
-    <row r="320" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="320" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C320" s="4"/>
     </row>
-    <row r="321" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="321" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C321" s="4"/>
     </row>
-    <row r="322" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="322" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C322" s="4"/>
     </row>
-    <row r="323" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="323" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C323" s="4"/>
     </row>
-    <row r="324" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="324" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C324" s="4"/>
     </row>
-    <row r="325" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="325" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C325" s="4"/>
     </row>
-    <row r="326" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="326" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C326" s="4"/>
     </row>
-    <row r="327" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="327" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C327" s="4"/>
     </row>
-    <row r="328" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="328" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C328" s="4"/>
     </row>
-    <row r="329" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="329" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C329" s="4"/>
     </row>
-    <row r="330" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="330" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C330" s="4"/>
     </row>
-    <row r="331" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="331" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C331" s="4"/>
     </row>
-    <row r="332" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="332" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C332" s="4"/>
     </row>
-    <row r="333" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="333" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C333" s="4"/>
     </row>
-    <row r="334" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="334" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C334" s="4"/>
     </row>
-    <row r="335" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="335" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C335" s="4"/>
     </row>
-    <row r="336" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="336" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C336" s="4"/>
     </row>
-    <row r="337" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="337" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C337" s="4"/>
     </row>
-    <row r="338" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="338" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C338" s="4"/>
     </row>
-    <row r="339" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="339" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C339" s="4"/>
     </row>
-    <row r="340" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="340" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C340" s="4"/>
     </row>
-    <row r="341" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="341" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C341" s="4"/>
     </row>
-    <row r="342" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="342" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C342" s="4"/>
     </row>
-    <row r="343" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="343" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C343" s="4"/>
     </row>
-    <row r="344" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="344" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C344" s="4"/>
     </row>
-    <row r="345" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="345" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C345" s="4"/>
     </row>
-    <row r="346" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="346" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C346" s="4"/>
     </row>
-    <row r="347" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="347" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C347" s="4"/>
     </row>
-    <row r="348" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="348" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C348" s="4"/>
     </row>
-    <row r="349" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="349" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C349" s="4"/>
     </row>
-    <row r="350" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="350" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C350" s="4"/>
     </row>
-    <row r="351" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="351" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C351" s="4"/>
     </row>
-    <row r="352" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="352" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C352" s="4"/>
     </row>
-    <row r="353" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="353" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C353" s="4"/>
     </row>
-    <row r="354" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="354" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C354" s="4"/>
     </row>
-    <row r="355" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="355" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C355" s="4"/>
     </row>
-    <row r="356" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="356" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C356" s="4"/>
     </row>
-    <row r="357" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="357" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C357" s="4"/>
     </row>
-    <row r="358" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="358" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C358" s="4"/>
     </row>
-    <row r="359" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="359" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C359" s="4"/>
     </row>
-    <row r="360" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="360" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C360" s="4"/>
     </row>
-    <row r="361" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="361" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C361" s="4"/>
     </row>
-    <row r="362" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="362" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C362" s="4"/>
     </row>
-    <row r="363" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="363" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C363" s="4"/>
     </row>
-    <row r="364" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="364" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C364" s="4"/>
     </row>
-    <row r="365" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="365" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C365" s="4"/>
     </row>
-    <row r="366" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="366" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C366" s="4"/>
     </row>
-    <row r="367" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="367" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C367" s="4"/>
     </row>
-    <row r="368" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="368" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C368" s="4"/>
     </row>
-    <row r="369" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="369" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C369" s="4"/>
     </row>
-    <row r="370" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="370" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C370" s="4"/>
     </row>
-    <row r="371" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="371" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C371" s="4"/>
     </row>
-    <row r="372" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="372" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C372" s="4"/>
     </row>
-    <row r="373" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="373" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C373" s="4"/>
     </row>
-    <row r="374" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="374" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C374" s="4"/>
     </row>
-    <row r="375" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="375" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C375" s="4"/>
     </row>
-    <row r="376" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="376" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C376" s="4"/>
     </row>
-    <row r="377" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="377" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C377" s="4"/>
     </row>
-    <row r="378" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="378" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C378" s="4"/>
     </row>
-    <row r="379" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="379" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C379" s="4"/>
     </row>
-    <row r="380" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="380" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C380" s="4"/>
     </row>
-    <row r="381" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="381" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C381" s="4"/>
     </row>
-    <row r="382" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="382" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C382" s="4"/>
     </row>
-    <row r="383" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="383" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C383" s="4"/>
     </row>
-    <row r="384" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="384" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C384" s="4"/>
     </row>
-    <row r="385" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="385" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C385" s="4"/>
     </row>
-    <row r="386" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="386" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C386" s="4"/>
     </row>
-    <row r="387" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="387" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C387" s="4"/>
     </row>
-    <row r="388" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="388" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C388" s="4"/>
     </row>
-    <row r="389" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="389" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C389" s="4"/>
     </row>
-    <row r="390" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="390" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C390" s="4"/>
     </row>
-    <row r="391" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="391" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C391" s="4"/>
     </row>
-    <row r="392" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="392" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C392" s="4"/>
     </row>
-    <row r="393" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="393" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C393" s="4"/>
     </row>
-    <row r="394" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="394" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C394" s="4"/>
     </row>
-    <row r="395" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="395" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C395" s="4"/>
     </row>
-    <row r="396" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="396" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C396" s="4"/>
     </row>
-    <row r="397" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="397" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C397" s="4"/>
     </row>
-    <row r="398" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="398" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C398" s="4"/>
     </row>
-    <row r="399" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="399" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C399" s="4"/>
     </row>
-    <row r="400" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="400" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C400" s="4"/>
     </row>
-    <row r="401" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="401" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C401" s="4"/>
     </row>
-    <row r="402" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="402" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C402" s="4"/>
     </row>
-    <row r="403" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="403" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C403" s="4"/>
     </row>
-    <row r="404" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="404" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C404" s="4"/>
     </row>
-    <row r="405" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="405" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C405" s="4"/>
     </row>
-    <row r="406" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="406" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C406" s="4"/>
     </row>
-    <row r="407" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="407" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C407" s="4"/>
     </row>
-    <row r="408" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="408" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C408" s="4"/>
     </row>
-    <row r="409" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="409" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C409" s="4"/>
     </row>
-    <row r="410" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="410" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C410" s="4"/>
     </row>
-    <row r="411" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="411" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C411" s="4"/>
     </row>
-    <row r="412" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="412" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C412" s="4"/>
     </row>
-    <row r="413" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="413" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C413" s="4"/>
     </row>
-    <row r="414" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="414" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C414" s="4"/>
     </row>
-    <row r="415" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="415" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C415" s="4"/>
     </row>
-    <row r="416" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="416" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C416" s="4"/>
     </row>
-    <row r="417" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="417" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C417" s="4"/>
     </row>
-    <row r="418" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="418" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C418" s="4"/>
     </row>
-    <row r="419" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="419" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C419" s="4"/>
     </row>
-    <row r="420" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="420" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C420" s="4"/>
     </row>
-    <row r="421" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="421" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C421" s="4"/>
     </row>
-    <row r="422" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="422" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C422" s="4"/>
     </row>
-    <row r="423" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="423" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C423" s="4"/>
     </row>
-    <row r="424" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="424" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C424" s="4"/>
     </row>
-    <row r="425" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="425" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C425" s="4"/>
     </row>
-    <row r="426" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="426" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C426" s="4"/>
     </row>
-    <row r="427" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="427" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C427" s="4"/>
     </row>
-    <row r="428" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="428" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C428" s="4"/>
     </row>
-    <row r="429" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="429" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C429" s="4"/>
     </row>
-    <row r="430" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="430" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C430" s="4"/>
     </row>
-    <row r="431" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="431" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C431" s="4"/>
     </row>
-    <row r="432" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="432" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C432" s="4"/>
     </row>
-    <row r="433" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="433" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C433" s="4"/>
     </row>
-    <row r="434" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="434" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C434" s="4"/>
     </row>
-    <row r="435" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="435" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C435" s="4"/>
     </row>
-    <row r="436" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="436" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C436" s="4"/>
     </row>
-    <row r="437" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="437" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C437" s="4"/>
     </row>
-    <row r="438" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="438" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C438" s="4"/>
     </row>
-    <row r="439" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="439" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C439" s="4"/>
     </row>
-    <row r="440" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="440" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C440" s="4"/>
     </row>
-    <row r="441" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="441" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C441" s="4"/>
     </row>
-    <row r="442" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="442" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C442" s="4"/>
     </row>
-    <row r="443" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="443" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C443" s="4"/>
     </row>
-    <row r="444" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="444" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C444" s="4"/>
     </row>
-    <row r="445" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="445" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C445" s="4"/>
     </row>
-    <row r="446" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="446" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C446" s="4"/>
     </row>
-    <row r="447" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="447" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C447" s="4"/>
     </row>
-    <row r="448" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="448" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C448" s="4"/>
     </row>
-    <row r="449" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="449" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C449" s="4"/>
     </row>
-    <row r="450" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="450" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C450" s="4"/>
     </row>
-    <row r="451" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="451" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C451" s="4"/>
     </row>
-    <row r="452" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="452" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C452" s="4"/>
     </row>
-    <row r="453" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="453" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C453" s="4"/>
     </row>
-    <row r="454" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="454" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C454" s="4"/>
     </row>
-    <row r="455" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="455" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C455" s="4"/>
     </row>
-    <row r="456" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="456" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C456" s="4"/>
     </row>
-    <row r="457" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="457" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C457" s="4"/>
     </row>
-    <row r="458" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="458" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C458" s="4"/>
     </row>
-    <row r="459" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="459" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C459" s="4"/>
     </row>
-    <row r="460" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="460" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C460" s="4"/>
     </row>
-    <row r="461" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="461" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C461" s="4"/>
     </row>
-    <row r="462" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="462" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C462" s="4"/>
     </row>
-    <row r="463" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="463" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C463" s="4"/>
     </row>
-    <row r="464" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="464" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C464" s="4"/>
     </row>
-    <row r="465" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="465" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C465" s="4"/>
     </row>
-    <row r="466" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="466" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C466" s="4"/>
     </row>
-    <row r="467" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="467" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C467" s="4"/>
     </row>
-    <row r="468" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="468" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C468" s="4"/>
     </row>
-    <row r="469" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="469" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C469" s="4"/>
     </row>
-    <row r="470" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="470" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C470" s="4"/>
     </row>
-    <row r="471" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="471" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C471" s="4"/>
     </row>
-    <row r="472" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="472" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C472" s="4"/>
     </row>
-    <row r="473" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="473" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C473" s="4"/>
     </row>
-    <row r="474" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="474" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C474" s="4"/>
     </row>
-    <row r="475" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="475" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C475" s="4"/>
     </row>
-    <row r="476" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="476" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C476" s="4"/>
     </row>
-    <row r="477" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="477" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C477" s="4"/>
     </row>
-    <row r="478" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="478" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C478" s="4"/>
     </row>
-    <row r="479" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="479" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C479" s="4"/>
     </row>
-    <row r="480" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="480" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C480" s="4"/>
     </row>
-    <row r="481" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="481" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C481" s="4"/>
     </row>
-    <row r="482" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="482" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C482" s="4"/>
     </row>
-    <row r="483" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="483" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C483" s="4"/>
     </row>
-    <row r="484" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="484" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C484" s="4"/>
     </row>
-    <row r="485" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="485" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C485" s="4"/>
     </row>
-    <row r="486" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="486" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C486" s="4"/>
     </row>
-    <row r="487" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="487" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C487" s="4"/>
     </row>
-    <row r="488" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="488" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C488" s="4"/>
     </row>
-    <row r="489" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="489" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C489" s="4"/>
     </row>
-    <row r="490" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="490" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C490" s="4"/>
     </row>
-    <row r="491" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="491" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C491" s="4"/>
     </row>
-    <row r="492" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="492" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C492" s="4"/>
     </row>
-    <row r="493" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="493" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C493" s="4"/>
     </row>
-    <row r="494" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="494" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C494" s="4"/>
     </row>
-    <row r="495" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="495" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C495" s="4"/>
     </row>
-    <row r="496" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="496" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C496" s="4"/>
     </row>
-    <row r="497" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="497" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C497" s="4"/>
     </row>
-    <row r="498" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="498" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C498" s="4"/>
     </row>
-    <row r="499" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="499" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C499" s="4"/>
     </row>
-    <row r="500" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="500" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C500" s="4"/>
     </row>
-    <row r="501" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="501" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C501" s="4"/>
     </row>
-    <row r="502" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="502" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C502" s="4"/>
     </row>
-    <row r="503" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="503" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C503" s="4"/>
     </row>
-    <row r="504" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="504" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C504" s="4"/>
     </row>
-    <row r="505" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="505" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C505" s="4"/>
     </row>
-    <row r="506" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="506" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C506" s="4"/>
     </row>
-    <row r="507" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="507" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C507" s="4"/>
     </row>
-    <row r="508" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="508" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C508" s="4"/>
     </row>
-    <row r="509" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="509" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C509" s="4"/>
     </row>
-    <row r="510" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="510" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C510" s="4"/>
     </row>
-    <row r="511" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="511" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C511" s="4"/>
     </row>
-    <row r="512" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="512" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C512" s="4"/>
     </row>
-    <row r="513" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="513" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C513" s="4"/>
     </row>
-    <row r="514" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="514" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C514" s="4"/>
     </row>
-    <row r="515" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="515" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C515" s="4"/>
     </row>
-    <row r="516" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="516" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C516" s="4"/>
     </row>
-    <row r="517" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="517" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C517" s="4"/>
     </row>
-    <row r="518" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="518" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C518" s="4"/>
     </row>
-    <row r="519" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="519" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C519" s="4"/>
     </row>
-    <row r="520" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="520" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C520" s="4"/>
     </row>
-    <row r="521" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="521" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C521" s="4"/>
     </row>
-    <row r="522" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="522" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C522" s="4"/>
     </row>
-    <row r="523" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="523" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C523" s="4"/>
     </row>
-    <row r="524" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="524" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C524" s="4"/>
     </row>
-    <row r="525" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="525" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C525" s="4"/>
     </row>
-    <row r="526" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="526" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C526" s="4"/>
     </row>
-    <row r="527" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="527" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C527" s="4"/>
     </row>
-    <row r="528" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="528" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C528" s="4"/>
     </row>
-    <row r="529" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="529" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C529" s="4"/>
     </row>
-    <row r="530" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="530" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C530" s="4"/>
     </row>
-    <row r="531" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="531" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C531" s="4"/>
     </row>
-    <row r="532" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="532" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C532" s="4"/>
     </row>
-    <row r="533" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="533" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C533" s="4"/>
     </row>
-    <row r="534" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="534" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C534" s="4"/>
     </row>
-    <row r="535" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="535" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C535" s="4"/>
     </row>
-    <row r="536" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="536" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C536" s="4"/>
     </row>
-    <row r="537" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="537" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C537" s="4"/>
     </row>
-    <row r="538" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="538" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C538" s="4"/>
     </row>
-    <row r="539" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="539" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C539" s="4"/>
     </row>
-    <row r="540" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="540" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C540" s="4"/>
     </row>
-    <row r="541" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="541" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C541" s="4"/>
     </row>
-    <row r="542" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="542" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C542" s="4"/>
     </row>
-    <row r="543" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="543" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C543" s="4"/>
     </row>
-    <row r="544" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="544" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C544" s="4"/>
     </row>
-    <row r="545" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="545" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C545" s="4"/>
     </row>
-    <row r="546" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="546" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C546" s="4"/>
     </row>
-    <row r="547" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="547" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C547" s="4"/>
     </row>
-    <row r="548" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="548" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C548" s="4"/>
     </row>
-    <row r="549" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="549" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C549" s="4"/>
     </row>
-    <row r="550" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="550" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C550" s="4"/>
     </row>
-    <row r="551" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="551" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C551" s="4"/>
     </row>
-    <row r="552" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="552" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C552" s="4"/>
     </row>
-    <row r="553" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="553" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C553" s="4"/>
     </row>
-    <row r="554" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="554" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C554" s="4"/>
     </row>
-    <row r="555" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="555" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C555" s="4"/>
     </row>
-    <row r="556" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="556" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C556" s="4"/>
     </row>
-    <row r="557" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="557" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C557" s="4"/>
     </row>
-    <row r="558" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="558" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C558" s="4"/>
     </row>
-    <row r="559" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="559" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C559" s="4"/>
     </row>
-    <row r="560" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="560" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C560" s="4"/>
     </row>
-    <row r="561" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="561" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C561" s="4"/>
     </row>
-    <row r="562" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="562" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C562" s="4"/>
     </row>
-    <row r="563" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="563" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C563" s="4"/>
     </row>
-    <row r="564" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="564" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C564" s="4"/>
     </row>
-    <row r="565" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="565" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C565" s="4"/>
     </row>
-    <row r="566" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="566" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C566" s="4"/>
     </row>
-    <row r="567" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="567" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C567" s="4"/>
     </row>
-    <row r="568" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="568" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C568" s="4"/>
     </row>
-    <row r="569" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="569" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C569" s="4"/>
     </row>
-    <row r="570" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="570" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C570" s="4"/>
     </row>
-    <row r="571" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="571" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C571" s="4"/>
     </row>
-    <row r="572" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="572" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C572" s="4"/>
     </row>
-    <row r="573" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="573" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C573" s="4"/>
     </row>
-    <row r="574" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="574" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C574" s="4"/>
     </row>
-    <row r="575" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="575" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C575" s="4"/>
     </row>
-    <row r="576" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="576" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C576" s="4"/>
     </row>
-    <row r="577" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="577" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C577" s="4"/>
     </row>
-    <row r="578" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="578" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C578" s="4"/>
     </row>
-    <row r="579" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="579" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C579" s="4"/>
     </row>
-    <row r="580" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="580" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C580" s="4"/>
     </row>
-    <row r="581" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="581" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C581" s="4"/>
     </row>
-    <row r="582" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="582" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C582" s="4"/>
     </row>
-    <row r="583" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="583" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C583" s="4"/>
     </row>
-    <row r="584" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="584" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C584" s="4"/>
     </row>
-    <row r="585" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="585" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C585" s="4"/>
     </row>
-    <row r="586" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="586" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C586" s="4"/>
     </row>
-    <row r="587" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="587" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C587" s="4"/>
     </row>
-    <row r="588" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="588" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C588" s="4"/>
     </row>
-    <row r="589" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="589" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C589" s="4"/>
     </row>
-    <row r="590" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="590" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C590" s="4"/>
     </row>
-    <row r="591" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="591" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C591" s="4"/>
     </row>
-    <row r="592" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="592" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C592" s="4"/>
     </row>
-    <row r="593" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="593" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C593" s="4"/>
     </row>
-    <row r="594" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="594" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C594" s="4"/>
     </row>
-    <row r="595" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="595" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C595" s="4"/>
     </row>
-    <row r="596" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="596" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C596" s="4"/>
     </row>
-    <row r="597" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="597" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C597" s="4"/>
     </row>
-    <row r="598" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="598" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C598" s="4"/>
     </row>
-    <row r="599" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="599" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C599" s="4"/>
     </row>
-    <row r="600" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="600" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C600" s="4"/>
     </row>
-    <row r="601" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="601" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C601" s="4"/>
     </row>
-    <row r="602" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="602" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C602" s="4"/>
     </row>
-    <row r="603" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="603" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C603" s="4"/>
     </row>
-    <row r="604" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="604" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C604" s="4"/>
     </row>
-    <row r="605" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="605" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C605" s="4"/>
     </row>
-    <row r="606" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="606" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C606" s="4"/>
     </row>
-    <row r="607" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="607" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C607" s="4"/>
     </row>
-    <row r="608" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="608" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C608" s="4"/>
     </row>
-    <row r="609" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="609" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C609" s="4"/>
     </row>
-    <row r="610" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="610" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C610" s="4"/>
     </row>
-    <row r="611" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="611" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C611" s="4"/>
     </row>
-    <row r="612" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="612" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C612" s="4"/>
     </row>
-    <row r="613" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="613" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C613" s="4"/>
     </row>
-    <row r="614" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="614" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C614" s="4"/>
     </row>
-    <row r="615" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="615" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C615" s="4"/>
     </row>
-    <row r="616" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="616" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C616" s="4"/>
     </row>
-    <row r="617" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="617" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C617" s="4"/>
     </row>
-    <row r="618" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="618" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C618" s="4"/>
     </row>
-    <row r="619" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="619" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C619" s="4"/>
     </row>
-    <row r="620" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="620" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C620" s="4"/>
     </row>
-    <row r="621" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="621" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C621" s="4"/>
     </row>
-    <row r="622" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="622" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C622" s="4"/>
     </row>
-    <row r="623" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="623" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C623" s="4"/>
     </row>
-    <row r="624" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="624" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C624" s="4"/>
     </row>
-    <row r="625" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="625" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C625" s="4"/>
     </row>
-    <row r="626" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="626" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C626" s="4"/>
     </row>
-    <row r="627" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="627" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C627" s="4"/>
     </row>
-    <row r="628" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="628" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C628" s="4"/>
     </row>
-    <row r="629" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="629" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C629" s="4"/>
     </row>
-    <row r="630" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="630" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C630" s="4"/>
     </row>
-    <row r="631" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="631" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C631" s="4"/>
     </row>
-    <row r="632" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="632" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C632" s="4"/>
     </row>
-    <row r="633" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="633" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C633" s="4"/>
     </row>
-    <row r="634" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="634" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C634" s="4"/>
     </row>
-    <row r="635" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="635" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C635" s="4"/>
     </row>
-    <row r="636" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="636" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C636" s="4"/>
     </row>
-    <row r="637" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="637" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C637" s="4"/>
     </row>
-    <row r="638" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="638" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C638" s="4"/>
     </row>
-    <row r="639" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="639" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C639" s="4"/>
     </row>
-    <row r="640" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="640" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C640" s="4"/>
     </row>
-    <row r="641" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="641" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C641" s="4"/>
     </row>
-    <row r="642" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="642" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C642" s="4"/>
     </row>
-    <row r="643" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="643" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C643" s="4"/>
     </row>
-    <row r="644" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="644" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C644" s="4"/>
     </row>
-    <row r="645" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="645" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C645" s="4"/>
     </row>
-    <row r="646" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="646" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C646" s="4"/>
     </row>
-    <row r="647" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="647" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C647" s="4"/>
     </row>
-    <row r="648" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="648" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C648" s="4"/>
     </row>
-    <row r="649" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="649" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C649" s="4"/>
     </row>
-    <row r="650" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="650" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C650" s="4"/>
     </row>
-    <row r="651" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="651" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C651" s="4"/>
     </row>
-    <row r="652" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="652" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C652" s="4"/>
     </row>
-    <row r="653" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="653" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C653" s="4"/>
     </row>
-    <row r="654" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="654" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C654" s="4"/>
     </row>
-    <row r="655" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="655" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C655" s="4"/>
     </row>
-    <row r="656" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="656" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C656" s="4"/>
     </row>
-    <row r="657" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="657" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C657" s="4"/>
     </row>
-    <row r="658" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="658" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C658" s="4"/>
     </row>
-    <row r="659" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="659" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C659" s="4"/>
     </row>
-    <row r="660" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="660" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C660" s="4"/>
     </row>
-    <row r="661" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="661" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C661" s="4"/>
     </row>
-    <row r="662" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="662" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C662" s="4"/>
     </row>
-    <row r="663" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="663" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C663" s="4"/>
     </row>
-    <row r="664" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="664" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C664" s="4"/>
     </row>
-    <row r="665" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="665" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C665" s="4"/>
     </row>
-    <row r="666" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="666" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C666" s="4"/>
     </row>
-    <row r="667" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="667" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C667" s="4"/>
     </row>
-    <row r="668" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="668" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C668" s="4"/>
     </row>
-    <row r="669" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="669" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C669" s="4"/>
     </row>
-    <row r="670" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="670" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C670" s="4"/>
     </row>
-    <row r="671" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="671" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C671" s="4"/>
     </row>
-    <row r="672" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="672" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C672" s="4"/>
     </row>
-    <row r="673" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="673" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C673" s="4"/>
     </row>
-    <row r="674" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="674" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C674" s="4"/>
     </row>
-    <row r="675" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="675" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C675" s="4"/>
     </row>
-    <row r="676" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="676" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C676" s="4"/>
     </row>
-    <row r="677" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="677" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C677" s="4"/>
     </row>
-    <row r="678" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="678" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C678" s="4"/>
     </row>
-    <row r="679" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="679" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C679" s="4"/>
     </row>
-    <row r="680" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="680" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C680" s="4"/>
     </row>
-    <row r="681" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="681" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C681" s="4"/>
     </row>
-    <row r="682" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="682" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C682" s="4"/>
     </row>
-    <row r="683" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="683" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C683" s="4"/>
     </row>
-    <row r="684" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="684" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C684" s="4"/>
     </row>
-    <row r="685" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="685" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C685" s="4"/>
     </row>
-    <row r="686" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="686" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C686" s="4"/>
     </row>
-    <row r="687" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="687" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C687" s="4"/>
     </row>
-    <row r="688" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="688" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C688" s="4"/>
     </row>
-    <row r="689" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="689" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C689" s="4"/>
     </row>
-    <row r="690" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="690" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C690" s="4"/>
     </row>
-    <row r="691" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="691" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C691" s="4"/>
     </row>
-    <row r="692" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="692" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C692" s="4"/>
     </row>
-    <row r="693" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="693" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C693" s="4"/>
     </row>
-    <row r="694" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="694" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C694" s="4"/>
     </row>
-    <row r="695" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="695" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C695" s="4"/>
     </row>
-    <row r="696" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="696" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C696" s="4"/>
     </row>
-    <row r="697" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="697" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C697" s="4"/>
     </row>
-    <row r="698" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="698" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C698" s="4"/>
     </row>
-    <row r="699" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="699" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C699" s="4"/>
     </row>
-    <row r="700" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="700" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C700" s="4"/>
     </row>
-    <row r="701" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="701" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C701" s="4"/>
     </row>
-    <row r="702" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="702" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C702" s="4"/>
     </row>
-    <row r="703" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="703" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C703" s="4"/>
     </row>
-    <row r="704" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="704" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C704" s="4"/>
     </row>
-    <row r="705" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="705" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C705" s="4"/>
     </row>
-    <row r="706" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="706" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C706" s="4"/>
     </row>
-    <row r="707" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="707" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C707" s="4"/>
     </row>
-    <row r="708" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="708" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C708" s="4"/>
     </row>
-    <row r="709" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="709" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C709" s="4"/>
     </row>
-    <row r="710" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="710" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C710" s="4"/>
     </row>
-    <row r="711" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="711" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C711" s="4"/>
     </row>
-    <row r="712" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="712" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C712" s="4"/>
     </row>
-    <row r="713" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="713" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C713" s="4"/>
     </row>
-    <row r="714" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="714" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C714" s="4"/>
     </row>
-    <row r="715" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="715" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C715" s="4"/>
     </row>
-    <row r="716" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="716" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C716" s="4"/>
     </row>
-    <row r="717" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="717" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C717" s="4"/>
     </row>
-    <row r="718" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="718" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C718" s="4"/>
     </row>
-    <row r="719" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="719" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C719" s="4"/>
     </row>
-    <row r="720" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="720" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C720" s="4"/>
     </row>
-    <row r="721" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="721" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C721" s="4"/>
     </row>
-    <row r="722" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="722" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C722" s="4"/>
     </row>
-    <row r="723" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="723" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C723" s="4"/>
     </row>
-    <row r="724" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="724" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C724" s="4"/>
     </row>
-    <row r="725" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="725" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C725" s="4"/>
     </row>
-    <row r="726" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="726" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C726" s="4"/>
     </row>
-    <row r="727" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="727" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C727" s="4"/>
     </row>
-    <row r="728" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="728" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C728" s="4"/>
     </row>
-    <row r="729" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="729" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C729" s="4"/>
     </row>
-    <row r="730" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="730" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C730" s="4"/>
     </row>
-    <row r="731" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="731" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C731" s="4"/>
     </row>
-    <row r="732" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="732" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C732" s="4"/>
     </row>
-    <row r="733" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="733" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C733" s="4"/>
     </row>
-    <row r="734" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="734" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C734" s="4"/>
     </row>
-    <row r="735" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="735" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C735" s="4"/>
     </row>
-    <row r="736" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="736" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C736" s="4"/>
     </row>
-    <row r="737" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="737" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C737" s="4"/>
     </row>
-    <row r="738" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="738" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C738" s="4"/>
     </row>
-    <row r="739" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="739" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C739" s="4"/>
     </row>
-    <row r="740" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="740" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C740" s="4"/>
     </row>
-    <row r="741" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="741" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C741" s="4"/>
     </row>
-    <row r="742" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="742" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C742" s="4"/>
     </row>
-    <row r="743" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="743" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C743" s="4"/>
     </row>
-    <row r="744" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="744" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C744" s="4"/>
     </row>
-    <row r="745" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="745" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C745" s="4"/>
     </row>
-    <row r="746" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="746" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C746" s="4"/>
     </row>
-    <row r="747" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="747" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C747" s="4"/>
     </row>
-    <row r="748" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="748" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C748" s="4"/>
     </row>
-    <row r="749" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="749" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C749" s="4"/>
     </row>
-    <row r="750" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="750" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C750" s="4"/>
     </row>
-    <row r="751" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="751" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C751" s="4"/>
     </row>
-    <row r="752" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="752" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C752" s="4"/>
     </row>
-    <row r="753" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="753" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C753" s="4"/>
     </row>
-    <row r="754" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="754" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C754" s="4"/>
     </row>
-    <row r="755" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="755" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C755" s="4"/>
     </row>
-    <row r="756" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="756" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C756" s="4"/>
     </row>
-    <row r="757" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="757" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C757" s="4"/>
     </row>
-    <row r="758" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="758" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C758" s="4"/>
     </row>
-    <row r="759" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="759" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C759" s="4"/>
     </row>
-    <row r="760" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="760" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C760" s="4"/>
     </row>
-    <row r="761" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="761" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C761" s="4"/>
     </row>
-    <row r="762" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="762" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C762" s="4"/>
     </row>
-    <row r="763" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="763" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C763" s="4"/>
     </row>
-    <row r="764" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="764" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C764" s="4"/>
     </row>
-    <row r="765" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="765" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C765" s="4"/>
     </row>
-    <row r="766" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="766" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C766" s="4"/>
     </row>
-    <row r="767" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="767" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C767" s="4"/>
     </row>
-    <row r="768" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="768" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C768" s="4"/>
     </row>
-    <row r="769" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="769" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C769" s="4"/>
     </row>
-    <row r="770" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="770" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C770" s="4"/>
     </row>
-    <row r="771" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="771" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C771" s="4"/>
     </row>
-    <row r="772" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="772" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C772" s="4"/>
     </row>
-    <row r="773" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="773" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C773" s="4"/>
     </row>
-    <row r="774" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="774" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C774" s="4"/>
     </row>
-    <row r="775" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="775" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C775" s="4"/>
     </row>
-    <row r="776" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="776" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C776" s="4"/>
     </row>
-    <row r="777" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="777" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C777" s="4"/>
     </row>
-    <row r="778" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="778" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C778" s="4"/>
     </row>
-    <row r="779" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="779" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C779" s="4"/>
     </row>
-    <row r="780" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="780" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C780" s="4"/>
     </row>
-    <row r="781" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="781" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C781" s="4"/>
     </row>
-    <row r="782" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="782" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C782" s="4"/>
     </row>
-    <row r="783" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="783" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C783" s="4"/>
     </row>
-    <row r="784" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="784" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C784" s="4"/>
     </row>
-    <row r="785" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="785" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C785" s="4"/>
     </row>
-    <row r="786" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="786" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C786" s="4"/>
     </row>
-    <row r="787" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="787" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C787" s="4"/>
     </row>
-    <row r="788" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="788" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C788" s="4"/>
     </row>
-    <row r="789" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="789" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C789" s="4"/>
     </row>
-    <row r="790" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="790" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C790" s="4"/>
     </row>
-    <row r="791" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="791" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C791" s="4"/>
     </row>
-    <row r="792" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="792" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C792" s="4"/>
     </row>
-    <row r="793" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="793" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C793" s="4"/>
     </row>
-    <row r="794" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="794" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C794" s="4"/>
     </row>
-    <row r="795" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="795" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C795" s="4"/>
     </row>
-    <row r="796" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="796" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C796" s="4"/>
     </row>
-    <row r="797" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="797" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C797" s="4"/>
     </row>
-    <row r="798" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="798" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C798" s="4"/>
     </row>
-    <row r="799" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="799" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C799" s="4"/>
     </row>
-    <row r="800" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="800" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C800" s="4"/>
     </row>
-    <row r="801" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="801" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C801" s="4"/>
     </row>
-    <row r="802" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="802" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C802" s="4"/>
     </row>
-    <row r="803" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="803" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C803" s="4"/>
     </row>
-    <row r="804" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="804" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C804" s="4"/>
     </row>
-    <row r="805" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="805" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C805" s="4"/>
     </row>
-    <row r="806" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="806" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C806" s="4"/>
     </row>
-    <row r="807" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="807" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C807" s="4"/>
     </row>
-    <row r="808" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="808" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C808" s="4"/>
     </row>
-    <row r="809" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="809" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C809" s="4"/>
     </row>
-    <row r="810" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="810" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C810" s="4"/>
     </row>
-    <row r="811" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="811" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C811" s="4"/>
     </row>
-    <row r="812" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="812" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C812" s="4"/>
     </row>
-    <row r="813" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="813" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C813" s="4"/>
     </row>
-    <row r="814" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="814" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C814" s="4"/>
     </row>
-    <row r="815" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="815" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C815" s="4"/>
     </row>
-    <row r="816" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="816" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C816" s="4"/>
     </row>
-    <row r="817" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="817" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C817" s="4"/>
     </row>
-    <row r="818" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="818" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C818" s="4"/>
     </row>
-    <row r="819" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="819" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C819" s="4"/>
     </row>
-    <row r="820" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="820" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C820" s="4"/>
     </row>
-    <row r="821" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="821" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C821" s="4"/>
     </row>
-    <row r="822" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="822" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C822" s="4"/>
     </row>
-    <row r="823" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="823" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C823" s="4"/>
     </row>
-    <row r="824" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="824" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C824" s="4"/>
     </row>
-    <row r="825" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="825" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C825" s="4"/>
     </row>
-    <row r="826" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="826" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C826" s="4"/>
     </row>
-    <row r="827" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="827" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C827" s="4"/>
     </row>
-    <row r="828" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="828" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C828" s="4"/>
     </row>
-    <row r="829" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="829" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C829" s="4"/>
     </row>
-    <row r="830" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="830" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C830" s="4"/>
     </row>
-    <row r="831" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="831" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C831" s="4"/>
     </row>
-    <row r="832" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="832" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C832" s="4"/>
     </row>
-    <row r="833" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="833" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C833" s="4"/>
     </row>
-    <row r="834" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="834" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C834" s="4"/>
     </row>
-    <row r="835" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="835" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C835" s="4"/>
     </row>
-    <row r="836" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="836" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C836" s="4"/>
     </row>
-    <row r="837" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="837" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C837" s="4"/>
     </row>
-    <row r="838" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="838" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C838" s="4"/>
     </row>
-    <row r="839" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="839" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C839" s="4"/>
     </row>
-    <row r="840" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="840" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C840" s="4"/>
     </row>
-    <row r="841" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="841" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C841" s="4"/>
     </row>
-    <row r="842" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="842" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C842" s="4"/>
     </row>
-    <row r="843" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="843" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C843" s="4"/>
     </row>
-    <row r="844" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="844" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C844" s="4"/>
     </row>
-    <row r="845" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="845" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C845" s="4"/>
     </row>
-    <row r="846" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="846" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C846" s="4"/>
     </row>
-    <row r="847" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="847" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C847" s="4"/>
     </row>
-    <row r="848" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="848" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C848" s="4"/>
     </row>
-    <row r="849" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="849" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C849" s="4"/>
     </row>
-    <row r="850" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="850" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C850" s="4"/>
     </row>
-    <row r="851" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="851" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C851" s="4"/>
     </row>
-    <row r="852" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="852" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C852" s="4"/>
     </row>
-    <row r="853" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="853" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C853" s="4"/>
     </row>
-    <row r="854" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="854" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C854" s="4"/>
     </row>
-    <row r="855" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="855" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C855" s="4"/>
     </row>
-    <row r="856" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="856" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C856" s="4"/>
     </row>
-    <row r="857" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="857" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C857" s="4"/>
     </row>
-    <row r="858" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="858" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C858" s="4"/>
     </row>
-    <row r="859" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="859" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C859" s="4"/>
     </row>
-    <row r="860" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="860" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C860" s="4"/>
     </row>
-    <row r="861" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="861" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C861" s="4"/>
     </row>
-    <row r="862" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="862" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C862" s="4"/>
     </row>
-    <row r="863" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="863" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C863" s="4"/>
     </row>
-    <row r="864" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="864" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C864" s="4"/>
     </row>
-    <row r="865" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="865" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C865" s="4"/>
     </row>
-    <row r="866" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="866" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C866" s="4"/>
     </row>
-    <row r="867" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="867" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C867" s="4"/>
     </row>
-    <row r="868" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="868" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C868" s="4"/>
     </row>
-    <row r="869" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="869" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C869" s="4"/>
     </row>
-    <row r="870" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="870" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C870" s="4"/>
     </row>
-    <row r="871" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="871" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C871" s="4"/>
     </row>
-    <row r="872" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="872" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C872" s="4"/>
     </row>
-    <row r="873" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="873" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C873" s="4"/>
     </row>
-    <row r="874" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="874" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C874" s="4"/>
     </row>
-    <row r="875" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="875" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C875" s="4"/>
     </row>
-    <row r="876" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="876" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C876" s="4"/>
     </row>
-    <row r="877" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="877" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C877" s="4"/>
     </row>
-    <row r="878" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="878" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C878" s="4"/>
     </row>
-    <row r="879" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="879" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C879" s="4"/>
     </row>
-    <row r="880" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="880" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C880" s="4"/>
     </row>
-    <row r="881" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="881" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C881" s="4"/>
     </row>
-    <row r="882" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="882" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C882" s="4"/>
     </row>
-    <row r="883" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="883" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C883" s="4"/>
     </row>
-    <row r="884" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="884" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C884" s="4"/>
     </row>
-    <row r="885" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="885" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C885" s="4"/>
     </row>
-    <row r="886" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="886" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C886" s="4"/>
     </row>
-    <row r="887" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="887" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C887" s="4"/>
     </row>
-    <row r="888" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="888" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C888" s="4"/>
     </row>
-    <row r="889" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="889" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C889" s="4"/>
     </row>
-    <row r="890" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="890" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C890" s="4"/>
     </row>
-    <row r="891" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="891" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C891" s="4"/>
     </row>
-    <row r="892" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="892" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C892" s="4"/>
     </row>
-    <row r="893" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="893" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C893" s="4"/>
     </row>
-    <row r="894" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="894" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C894" s="4"/>
     </row>
-    <row r="895" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="895" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C895" s="4"/>
     </row>
-    <row r="896" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="896" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C896" s="4"/>
     </row>
-    <row r="897" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="897" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C897" s="4"/>
     </row>
-    <row r="898" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="898" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C898" s="4"/>
     </row>
-    <row r="899" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="899" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C899" s="4"/>
     </row>
-    <row r="900" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="900" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C900" s="4"/>
     </row>
-    <row r="901" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="901" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C901" s="4"/>
     </row>
-    <row r="902" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="902" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C902" s="4"/>
     </row>
-    <row r="903" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="903" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C903" s="4"/>
     </row>
-    <row r="904" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="904" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C904" s="4"/>
     </row>
-    <row r="905" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="905" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C905" s="4"/>
     </row>
-    <row r="906" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="906" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C906" s="4"/>
     </row>
-    <row r="907" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="907" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C907" s="4"/>
     </row>
-    <row r="908" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="908" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C908" s="4"/>
     </row>
-    <row r="909" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="909" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C909" s="4"/>
     </row>
-    <row r="910" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="910" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C910" s="4"/>
     </row>
-    <row r="911" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="911" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C911" s="4"/>
     </row>
-    <row r="912" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="912" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C912" s="4"/>
     </row>
-    <row r="913" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="913" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C913" s="4"/>
     </row>
-    <row r="914" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="914" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C914" s="4"/>
     </row>
-    <row r="915" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="915" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C915" s="4"/>
     </row>
-    <row r="916" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="916" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C916" s="4"/>
     </row>
-    <row r="917" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="917" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C917" s="4"/>
     </row>
-    <row r="918" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="918" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C918" s="4"/>
     </row>
-    <row r="919" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="919" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C919" s="4"/>
     </row>
-    <row r="920" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="920" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C920" s="4"/>
     </row>
-    <row r="921" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="921" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C921" s="4"/>
     </row>
-    <row r="922" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="922" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C922" s="4"/>
     </row>
-    <row r="923" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="923" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C923" s="4"/>
     </row>
-    <row r="924" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="924" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C924" s="4"/>
     </row>
-    <row r="925" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="925" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C925" s="4"/>
     </row>
-    <row r="926" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="926" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C926" s="4"/>
     </row>
-    <row r="927" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="927" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C927" s="4"/>
     </row>
-    <row r="928" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="928" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C928" s="4"/>
     </row>
-    <row r="929" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="929" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C929" s="4"/>
     </row>
-    <row r="930" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="930" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C930" s="4"/>
     </row>
-    <row r="931" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="931" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C931" s="4"/>
     </row>
-    <row r="932" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="932" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C932" s="4"/>
     </row>
-    <row r="933" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="933" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C933" s="4"/>
     </row>
-    <row r="934" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="934" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C934" s="4"/>
     </row>
-    <row r="935" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="935" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C935" s="4"/>
     </row>
-    <row r="936" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="936" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C936" s="4"/>
     </row>
-    <row r="937" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="937" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C937" s="4"/>
     </row>
-    <row r="938" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="938" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C938" s="4"/>
     </row>
-    <row r="939" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="939" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C939" s="4"/>
     </row>
-    <row r="940" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="940" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C940" s="4"/>
     </row>
-    <row r="941" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="941" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C941" s="4"/>
     </row>
-    <row r="942" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="942" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C942" s="4"/>
     </row>
-    <row r="943" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="943" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C943" s="4"/>
     </row>
-    <row r="944" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="944" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C944" s="4"/>
     </row>
-    <row r="945" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="945" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C945" s="4"/>
     </row>
-    <row r="946" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="946" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C946" s="4"/>
     </row>
-    <row r="947" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="947" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C947" s="4"/>
     </row>
-    <row r="948" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="948" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C948" s="4"/>
     </row>
-    <row r="949" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="949" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C949" s="4"/>
     </row>
-    <row r="950" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="950" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C950" s="4"/>
     </row>
-    <row r="951" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="951" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C951" s="4"/>
     </row>
-    <row r="952" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="952" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C952" s="4"/>
     </row>
-    <row r="953" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="953" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C953" s="4"/>
     </row>
-    <row r="954" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="954" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C954" s="4"/>
     </row>
-    <row r="955" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="955" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C955" s="4"/>
     </row>
-    <row r="956" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="956" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C956" s="4"/>
     </row>
-    <row r="957" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="957" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C957" s="4"/>
     </row>
-    <row r="958" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="958" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C958" s="4"/>
     </row>
-    <row r="959" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="959" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C959" s="4"/>
     </row>
-    <row r="960" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="960" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C960" s="4"/>
     </row>
-    <row r="961" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="961" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C961" s="4"/>
     </row>
-    <row r="962" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="962" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C962" s="4"/>
     </row>
-    <row r="963" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="963" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C963" s="4"/>
     </row>
-    <row r="964" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="964" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C964" s="4"/>
     </row>
-    <row r="965" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="965" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C965" s="4"/>
     </row>
-    <row r="966" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="966" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C966" s="4"/>
     </row>
-    <row r="967" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="967" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C967" s="4"/>
     </row>
-    <row r="968" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="968" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C968" s="4"/>
     </row>
-    <row r="969" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="969" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C969" s="4"/>
     </row>
-    <row r="970" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="970" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C970" s="4"/>
     </row>
-    <row r="971" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="971" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C971" s="4"/>
     </row>
-    <row r="972" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="972" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C972" s="4"/>
     </row>
-    <row r="973" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="973" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C973" s="4"/>
     </row>
-    <row r="974" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="974" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C974" s="4"/>
     </row>
-    <row r="975" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="975" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C975" s="4"/>
     </row>
-    <row r="976" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="976" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C976" s="4"/>
     </row>
-    <row r="977" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="977" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C977" s="4"/>
     </row>
-    <row r="978" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="978" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C978" s="4"/>
     </row>
-    <row r="979" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="979" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C979" s="4"/>
     </row>
-    <row r="980" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="980" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C980" s="4"/>
     </row>
-    <row r="981" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="981" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C981" s="4"/>
     </row>
-    <row r="982" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="982" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C982" s="4"/>
     </row>
-    <row r="983" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="983" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C983" s="4"/>
     </row>
-    <row r="984" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="984" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C984" s="4"/>
     </row>
-    <row r="985" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="985" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C985" s="4"/>
     </row>
-    <row r="986" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="986" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C986" s="4"/>
     </row>
-    <row r="987" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="987" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C987" s="4"/>
     </row>
-    <row r="988" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="988" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C988" s="4"/>
     </row>
-    <row r="989" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="989" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C989" s="4"/>
     </row>
-    <row r="990" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="990" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C990" s="4"/>
     </row>
-    <row r="991" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="991" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C991" s="4"/>
     </row>
-    <row r="992" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="992" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C992" s="4"/>
     </row>
-    <row r="993" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="993" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C993" s="4"/>
     </row>
-    <row r="994" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="994" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C994" s="4"/>
     </row>
-    <row r="995" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="995" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C995" s="4"/>
     </row>
-    <row r="996" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="996" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C996" s="4"/>
     </row>
-    <row r="997" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="997" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C997" s="4"/>
     </row>
-    <row r="998" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="998" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C998" s="4"/>
     </row>
-    <row r="999" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="999" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C999" s="4"/>
     </row>
-    <row r="1000" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1000" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1000" s="4"/>
     </row>
-    <row r="1001" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1001" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1001" s="4"/>
     </row>
-    <row r="1002" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1002" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1002" s="4"/>
     </row>
-    <row r="1003" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1003" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1003" s="4"/>
     </row>
-    <row r="1004" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1004" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1004" s="4"/>
     </row>
-    <row r="1005" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1005" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1005" s="4"/>
     </row>
-    <row r="1006" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1006" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1006" s="4"/>
     </row>
-    <row r="1007" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1007" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1007" s="4"/>
     </row>
-    <row r="1008" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1008" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1008" s="4"/>
     </row>
-    <row r="1009" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1009" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1009" s="4"/>
     </row>
-    <row r="1010" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1010" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1010" s="4"/>
     </row>
-    <row r="1011" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1011" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1011" s="4"/>
     </row>
-    <row r="1012" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1012" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1012" s="4"/>
     </row>
-    <row r="1013" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1013" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1013" s="4"/>
     </row>
-    <row r="1014" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1014" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1014" s="4"/>
     </row>
-    <row r="1015" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1015" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1015" s="4"/>
     </row>
-    <row r="1016" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1016" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1016" s="4"/>
     </row>
-    <row r="1017" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1017" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1017" s="4"/>
     </row>
-    <row r="1018" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1018" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1018" s="4"/>
     </row>
-    <row r="1019" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1019" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1019" s="4"/>
     </row>
-    <row r="1020" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1020" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1020" s="4"/>
     </row>
-    <row r="1021" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1021" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1021" s="4"/>
     </row>
-    <row r="1022" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1022" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1022" s="4"/>
     </row>
-    <row r="1023" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1023" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1023" s="4"/>
     </row>
-    <row r="1024" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1024" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1024" s="4"/>
     </row>
-    <row r="1025" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1025" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1025" s="4"/>
     </row>
-    <row r="1026" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1026" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1026" s="4"/>
     </row>
-    <row r="1027" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1027" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1027" s="4"/>
     </row>
-    <row r="1028" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1028" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1028" s="4"/>
     </row>
-    <row r="1029" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1029" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1029" s="4"/>
     </row>
-    <row r="1030" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1030" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1030" s="4"/>
     </row>
-    <row r="1031" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1031" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1031" s="4"/>
     </row>
-    <row r="1032" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1032" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1032" s="4"/>
     </row>
-    <row r="1033" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1033" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1033" s="4"/>
     </row>
-    <row r="1034" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1034" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1034" s="4"/>
     </row>
-    <row r="1035" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1035" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1035" s="4"/>
     </row>
-    <row r="1036" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1036" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1036" s="4"/>
     </row>
-    <row r="1037" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1037" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1037" s="4"/>
     </row>
-    <row r="1038" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1038" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1038" s="4"/>
     </row>
-    <row r="1039" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1039" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1039" s="4"/>
     </row>
-    <row r="1040" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1040" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1040" s="4"/>
     </row>
-    <row r="1041" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1041" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1041" s="4"/>
     </row>
-    <row r="1042" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1042" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1042" s="4"/>
     </row>
-    <row r="1043" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1043" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1043" s="4"/>
     </row>
-    <row r="1044" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1044" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1044" s="4"/>
     </row>
-    <row r="1045" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1045" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1045" s="4"/>
     </row>
-    <row r="1046" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1046" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1046" s="4"/>
     </row>
-    <row r="1047" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1047" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1047" s="4"/>
     </row>
-    <row r="1048" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1048" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1048" s="4"/>
     </row>
-    <row r="1049" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1049" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1049" s="4"/>
     </row>
-    <row r="1050" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1050" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1050" s="4"/>
     </row>
-    <row r="1051" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1051" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1051" s="4"/>
     </row>
-    <row r="1052" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1052" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1052" s="4"/>
     </row>
-    <row r="1053" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1053" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1053" s="4"/>
     </row>
-    <row r="1054" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1054" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1054" s="4"/>
     </row>
-    <row r="1055" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1055" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1055" s="4"/>
     </row>
-    <row r="1056" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1056" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1056" s="4"/>
     </row>
-    <row r="1057" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1057" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1057" s="4"/>
     </row>
-    <row r="1058" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1058" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1058" s="4"/>
     </row>
-    <row r="1059" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1059" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1059" s="4"/>
     </row>
-    <row r="1060" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1060" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1060" s="4"/>
     </row>
-    <row r="1061" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1061" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1061" s="4"/>
     </row>
-    <row r="1062" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1062" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1062" s="4"/>
     </row>
-    <row r="1063" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1063" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1063" s="4"/>
     </row>
-    <row r="1064" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1064" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1064" s="4"/>
     </row>
-    <row r="1065" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1065" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1065" s="4"/>
     </row>
-    <row r="1066" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1066" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1066" s="4"/>
     </row>
-    <row r="1067" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1067" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1067" s="4"/>
     </row>
-    <row r="1068" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1068" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1068" s="4"/>
     </row>
-    <row r="1069" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1069" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1069" s="4"/>
     </row>
-    <row r="1070" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1070" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1070" s="4"/>
     </row>
-    <row r="1071" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1071" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1071" s="4"/>
     </row>
-    <row r="1072" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1072" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1072" s="4"/>
     </row>
-    <row r="1073" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1073" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1073" s="4"/>
     </row>
-    <row r="1074" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1074" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1074" s="4"/>
     </row>
-    <row r="1075" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1075" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1075" s="4"/>
     </row>
-    <row r="1076" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1076" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1076" s="4"/>
     </row>
-    <row r="1077" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1077" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1077" s="4"/>
     </row>
-    <row r="1078" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1078" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1078" s="4"/>
     </row>
-    <row r="1079" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1079" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1079" s="4"/>
     </row>
-    <row r="1080" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1080" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1080" s="4"/>
     </row>
-    <row r="1081" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1081" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1081" s="4"/>
     </row>
-    <row r="1082" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1082" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1082" s="4"/>
     </row>
-    <row r="1083" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1083" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1083" s="4"/>
     </row>
-    <row r="1084" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1084" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1084" s="4"/>
     </row>
-    <row r="1085" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1085" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1085" s="4"/>
     </row>
-    <row r="1086" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1086" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1086" s="4"/>
     </row>
-    <row r="1087" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1087" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1087" s="4"/>
     </row>
-    <row r="1088" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1088" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1088" s="4"/>
     </row>
-    <row r="1089" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1089" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1089" s="4"/>
     </row>
-    <row r="1090" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1090" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1090" s="4"/>
     </row>
-    <row r="1091" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1091" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1091" s="4"/>
     </row>
-    <row r="1092" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1092" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1092" s="4"/>
     </row>
-    <row r="1093" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1093" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1093" s="4"/>
     </row>
-    <row r="1094" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1094" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1094" s="4"/>
     </row>
-    <row r="1095" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1095" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1095" s="4"/>
     </row>
-    <row r="1096" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1096" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1096" s="4"/>
     </row>
-    <row r="1097" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1097" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1097" s="4"/>
     </row>
-    <row r="1098" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1098" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1098" s="4"/>
     </row>
-    <row r="1099" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1099" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1099" s="4"/>
     </row>
-    <row r="1100" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1100" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1100" s="4"/>
     </row>
-    <row r="1101" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1101" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1101" s="4"/>
     </row>
-    <row r="1102" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1102" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1102" s="4"/>
     </row>
-    <row r="1103" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1103" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1103" s="4"/>
     </row>
-    <row r="1104" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1104" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1104" s="4"/>
     </row>
-    <row r="1105" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1105" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1105" s="4"/>
     </row>
-    <row r="1106" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1106" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1106" s="4"/>
     </row>
-    <row r="1107" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1107" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1107" s="4"/>
     </row>
-    <row r="1108" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1108" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1108" s="4"/>
     </row>
-    <row r="1109" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1109" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1109" s="4"/>
     </row>
-    <row r="1110" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1110" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1110" s="4"/>
     </row>
-    <row r="1111" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1111" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1111" s="4"/>
     </row>
-    <row r="1112" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1112" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1112" s="4"/>
     </row>
-    <row r="1113" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1113" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1113" s="4"/>
     </row>
-    <row r="1114" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1114" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1114" s="4"/>
     </row>
-    <row r="1115" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1115" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1115" s="4"/>
     </row>
-    <row r="1116" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1116" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1116" s="4"/>
     </row>
-    <row r="1117" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1117" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1117" s="4"/>
     </row>
-    <row r="1118" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1118" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1118" s="4"/>
     </row>
-    <row r="1119" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1119" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1119" s="4"/>
     </row>
-    <row r="1120" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1120" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1120" s="4"/>
     </row>
-    <row r="1121" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1121" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1121" s="4"/>
     </row>
-    <row r="1122" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1122" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1122" s="4"/>
     </row>
-    <row r="1123" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1123" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1123" s="4"/>
     </row>
-    <row r="1124" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1124" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1124" s="4"/>
     </row>
-    <row r="1125" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1125" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1125" s="4"/>
     </row>
-    <row r="1126" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1126" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1126" s="4"/>
     </row>
-    <row r="1127" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1127" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1127" s="4"/>
     </row>
-    <row r="1128" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1128" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1128" s="4"/>
     </row>
-    <row r="1129" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1129" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1129" s="4"/>
     </row>
-    <row r="1130" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1130" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1130" s="4"/>
     </row>
-    <row r="1131" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1131" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1131" s="4"/>
     </row>
-    <row r="1132" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1132" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1132" s="4"/>
     </row>
-    <row r="1133" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1133" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1133" s="4"/>
     </row>
-    <row r="1134" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1134" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1134" s="4"/>
     </row>
-    <row r="1135" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1135" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1135" s="4"/>
     </row>
-    <row r="1136" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1136" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1136" s="4"/>
     </row>
-    <row r="1137" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1137" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1137" s="4"/>
     </row>
-    <row r="1138" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1138" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1138" s="4"/>
     </row>
-    <row r="1139" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1139" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1139" s="4"/>
     </row>
-    <row r="1140" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1140" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1140" s="4"/>
     </row>
-    <row r="1141" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1141" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1141" s="4"/>
     </row>
-    <row r="1142" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1142" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1142" s="4"/>
     </row>
-    <row r="1143" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1143" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1143" s="4"/>
     </row>
-    <row r="1144" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1144" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1144" s="4"/>
     </row>
-    <row r="1145" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1145" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1145" s="4"/>
     </row>
-    <row r="1146" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1146" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1146" s="4"/>
     </row>
-    <row r="1147" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1147" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1147" s="4"/>
     </row>
-    <row r="1148" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1148" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1148" s="4"/>
     </row>
-    <row r="1149" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1149" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1149" s="4"/>
     </row>
-    <row r="1150" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1150" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1150" s="4"/>
     </row>
-    <row r="1151" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1151" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1151" s="4"/>
     </row>
-    <row r="1152" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1152" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1152" s="4"/>
     </row>
-    <row r="1153" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1153" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1153" s="4"/>
     </row>
-    <row r="1154" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1154" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1154" s="4"/>
     </row>
-    <row r="1155" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1155" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1155" s="4"/>
     </row>
-    <row r="1156" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1156" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1156" s="4"/>
     </row>
-    <row r="1157" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1157" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1157" s="4"/>
     </row>
-    <row r="1158" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1158" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1158" s="4"/>
     </row>
-    <row r="1159" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1159" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1159" s="4"/>
     </row>
-    <row r="1160" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1160" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1160" s="4"/>
     </row>
-    <row r="1161" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1161" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1161" s="4"/>
     </row>
-    <row r="1162" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1162" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1162" s="4"/>
     </row>
-    <row r="1163" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1163" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1163" s="4"/>
     </row>
-    <row r="1164" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1164" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1164" s="4"/>
     </row>
-    <row r="1165" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1165" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1165" s="4"/>
     </row>
-    <row r="1166" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1166" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1166" s="4"/>
     </row>
-    <row r="1167" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1167" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1167" s="4"/>
     </row>
-    <row r="1168" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1168" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1168" s="4"/>
     </row>
-    <row r="1169" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1169" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1169" s="4"/>
     </row>
-    <row r="1170" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1170" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1170" s="4"/>
     </row>
-    <row r="1171" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1171" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1171" s="4"/>
     </row>
-    <row r="1172" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1172" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1172" s="4"/>
     </row>
-    <row r="1173" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1173" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1173" s="4"/>
     </row>
-    <row r="1174" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1174" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1174" s="4"/>
     </row>
-    <row r="1175" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1175" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1175" s="4"/>
     </row>
-    <row r="1176" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1176" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1176" s="4"/>
     </row>
-    <row r="1177" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1177" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1177" s="4"/>
     </row>
-    <row r="1178" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1178" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1178" s="4"/>
     </row>
-    <row r="1179" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1179" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1179" s="4"/>
     </row>
-    <row r="1180" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1180" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1180" s="4"/>
     </row>
-    <row r="1181" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1181" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1181" s="4"/>
     </row>
-    <row r="1182" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1182" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1182" s="4"/>
     </row>
-    <row r="1183" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1183" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1183" s="4"/>
     </row>
-    <row r="1184" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1184" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1184" s="4"/>
     </row>
-    <row r="1185" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1185" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1185" s="4"/>
     </row>
-    <row r="1186" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1186" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1186" s="4"/>
     </row>
-    <row r="1187" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1187" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1187" s="4"/>
     </row>
-    <row r="1188" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1188" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1188" s="4"/>
     </row>
-    <row r="1189" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1189" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1189" s="4"/>
     </row>
-    <row r="1190" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1190" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1190" s="4"/>
     </row>
-    <row r="1191" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1191" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1191" s="4"/>
     </row>
-    <row r="1192" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1192" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1192" s="4"/>
     </row>
-    <row r="1193" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1193" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1193" s="4"/>
     </row>
-    <row r="1194" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1194" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1194" s="4"/>
     </row>
-    <row r="1195" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1195" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1195" s="4"/>
     </row>
-    <row r="1196" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1196" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1196" s="4"/>
     </row>
-    <row r="1197" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1197" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1197" s="4"/>
     </row>
-    <row r="1198" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1198" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1198" s="4"/>
     </row>
-    <row r="1199" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1199" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1199" s="4"/>
     </row>
-    <row r="1200" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1200" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1200" s="4"/>
     </row>
-    <row r="1201" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1201" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1201" s="4"/>
     </row>
-    <row r="1202" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1202" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1202" s="4"/>
     </row>
-    <row r="1203" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1203" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1203" s="4"/>
     </row>
-    <row r="1204" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1204" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1204" s="4"/>
     </row>
-    <row r="1205" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1205" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1205" s="4"/>
     </row>
-    <row r="1206" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1206" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1206" s="4"/>
     </row>
-    <row r="1207" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1207" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1207" s="4"/>
     </row>
-    <row r="1208" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1208" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1208" s="4"/>
     </row>
-    <row r="1209" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1209" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1209" s="4"/>
     </row>
-    <row r="1210" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1210" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1210" s="4"/>
     </row>
-    <row r="1211" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1211" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1211" s="4"/>
     </row>
-    <row r="1212" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1212" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1212" s="4"/>
     </row>
-    <row r="1213" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1213" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1213" s="4"/>
     </row>
-    <row r="1214" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1214" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1214" s="4"/>
     </row>
-    <row r="1215" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1215" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1215" s="4"/>
     </row>
-    <row r="1216" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1216" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1216" s="4"/>
     </row>
-    <row r="1217" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1217" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1217" s="4"/>
     </row>
-    <row r="1218" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1218" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1218" s="4"/>
     </row>
-    <row r="1219" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1219" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1219" s="4"/>
     </row>
-    <row r="1220" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1220" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1220" s="4"/>
     </row>
-    <row r="1221" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1221" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1221" s="4"/>
     </row>
-    <row r="1222" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1222" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1222" s="4"/>
     </row>
-    <row r="1223" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1223" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1223" s="4"/>
     </row>
-    <row r="1224" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1224" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1224" s="4"/>
     </row>
-    <row r="1225" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1225" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1225" s="4"/>
     </row>
-    <row r="1226" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1226" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1226" s="4"/>
     </row>
-    <row r="1227" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1227" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1227" s="4"/>
     </row>
-    <row r="1228" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1228" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1228" s="4"/>
     </row>
-    <row r="1229" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1229" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1229" s="4"/>
     </row>
-    <row r="1230" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1230" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1230" s="4"/>
     </row>
-    <row r="1231" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1231" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1231" s="4"/>
     </row>
-    <row r="1232" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1232" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1232" s="4"/>
     </row>
-    <row r="1233" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1233" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1233" s="4"/>
     </row>
-    <row r="1234" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1234" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1234" s="4"/>
     </row>
-    <row r="1235" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1235" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1235" s="4"/>
     </row>
-    <row r="1236" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1236" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1236" s="4"/>
     </row>
-    <row r="1237" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1237" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1237" s="4"/>
     </row>
-    <row r="1238" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1238" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1238" s="4"/>
     </row>
-    <row r="1239" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1239" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1239" s="4"/>
     </row>
-    <row r="1240" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1240" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1240" s="4"/>
     </row>
-    <row r="1241" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1241" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1241" s="4"/>
     </row>
-    <row r="1242" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1242" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1242" s="4"/>
     </row>
-    <row r="1243" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1243" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1243" s="4"/>
     </row>
-    <row r="1244" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1244" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1244" s="4"/>
     </row>
-    <row r="1245" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1245" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1245" s="4"/>
     </row>
-    <row r="1246" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1246" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1246" s="4"/>
     </row>
-    <row r="1247" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1247" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1247" s="4"/>
     </row>
-    <row r="1248" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1248" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1248" s="4"/>
     </row>
-    <row r="1249" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1249" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1249" s="4"/>
     </row>
-    <row r="1250" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1250" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1250" s="4"/>
     </row>
-    <row r="1251" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1251" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1251" s="4"/>
     </row>
-    <row r="1252" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1252" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1252" s="4"/>
     </row>
-    <row r="1253" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1253" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1253" s="4"/>
     </row>
-    <row r="1254" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1254" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1254" s="4"/>
     </row>
-    <row r="1255" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1255" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1255" s="4"/>
     </row>
-    <row r="1256" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1256" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1256" s="4"/>
     </row>
-    <row r="1257" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1257" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1257" s="4"/>
     </row>
-    <row r="1258" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1258" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1258" s="4"/>
     </row>
-    <row r="1259" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1259" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1259" s="4"/>
     </row>
-    <row r="1260" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1260" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1260" s="4"/>
     </row>
-    <row r="1261" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1261" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1261" s="4"/>
     </row>
-    <row r="1262" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1262" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1262" s="4"/>
     </row>
-    <row r="1263" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1263" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1263" s="4"/>
     </row>
-    <row r="1264" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1264" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1264" s="4"/>
     </row>
-    <row r="1265" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1265" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1265" s="4"/>
     </row>
-    <row r="1266" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1266" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1266" s="4"/>
     </row>
-    <row r="1267" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1267" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1267" s="4"/>
     </row>
-    <row r="1268" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1268" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1268" s="4"/>
     </row>
-    <row r="1269" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1269" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1269" s="4"/>
     </row>
-    <row r="1270" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1270" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1270" s="4"/>
     </row>
-    <row r="1271" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1271" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1271" s="4"/>
     </row>
-    <row r="1272" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1272" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1272" s="4"/>
     </row>
-    <row r="1273" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1273" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1273" s="4"/>
     </row>
-    <row r="1274" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1274" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1274" s="4"/>
     </row>
-    <row r="1275" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1275" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1275" s="4"/>
     </row>
-    <row r="1276" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1276" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1276" s="4"/>
     </row>
-    <row r="1277" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1277" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1277" s="4"/>
     </row>
-    <row r="1278" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1278" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1278" s="4"/>
     </row>
-    <row r="1279" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1279" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1279" s="4"/>
     </row>
-    <row r="1280" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1280" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1280" s="4"/>
     </row>
-    <row r="1281" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1281" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1281" s="4"/>
     </row>
-    <row r="1282" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1282" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1282" s="4"/>
     </row>
-    <row r="1283" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1283" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1283" s="4"/>
     </row>
-    <row r="1284" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1284" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1284" s="4"/>
     </row>
-    <row r="1285" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1285" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1285" s="4"/>
     </row>
-    <row r="1286" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1286" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1286" s="4"/>
     </row>
-    <row r="1287" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1287" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1287" s="4"/>
     </row>
-    <row r="1288" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1288" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1288" s="4"/>
     </row>
-    <row r="1289" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1289" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1289" s="4"/>
     </row>
-    <row r="1290" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1290" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1290" s="4"/>
     </row>
-    <row r="1291" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1291" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1291" s="4"/>
     </row>
-    <row r="1292" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1292" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1292" s="4"/>
     </row>
-    <row r="1293" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1293" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1293" s="4"/>
     </row>
-    <row r="1294" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1294" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1294" s="4"/>
     </row>
-    <row r="1295" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1295" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1295" s="4"/>
     </row>
-    <row r="1296" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1296" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1296" s="4"/>
     </row>
-    <row r="1297" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1297" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1297" s="4"/>
     </row>
-    <row r="1298" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1298" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1298" s="4"/>
     </row>
-    <row r="1299" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1299" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1299" s="4"/>
     </row>
-    <row r="1300" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1300" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1300" s="4"/>
     </row>
-    <row r="1301" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1301" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1301" s="4"/>
     </row>
-    <row r="1302" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1302" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1302" s="4"/>
     </row>
-    <row r="1303" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1303" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1303" s="4"/>
     </row>
-    <row r="1304" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1304" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1304" s="4"/>
     </row>
-    <row r="1305" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1305" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1305" s="4"/>
     </row>
-    <row r="1306" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1306" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1306" s="4"/>
     </row>
-    <row r="1307" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1307" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1307" s="4"/>
     </row>
-    <row r="1308" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1308" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1308" s="4"/>
     </row>
-    <row r="1309" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1309" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1309" s="4"/>
     </row>
-    <row r="1310" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1310" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1310" s="4"/>
     </row>
-    <row r="1311" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1311" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1311" s="4"/>
     </row>
-    <row r="1312" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1312" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1312" s="4"/>
     </row>
-    <row r="1313" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1313" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1313" s="4"/>
     </row>
-    <row r="1314" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1314" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1314" s="4"/>
     </row>
-    <row r="1315" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1315" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1315" s="4"/>
     </row>
-    <row r="1316" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1316" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1316" s="4"/>
     </row>
-    <row r="1317" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1317" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1317" s="4"/>
     </row>
-    <row r="1318" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1318" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1318" s="4"/>
     </row>
-    <row r="1319" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1319" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1319" s="4"/>
     </row>
-    <row r="1320" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1320" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1320" s="4"/>
     </row>
-    <row r="1321" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1321" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1321" s="4"/>
     </row>
-    <row r="1322" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1322" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1322" s="4"/>
     </row>
-    <row r="1323" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1323" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1323" s="4"/>
     </row>
-    <row r="1324" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1324" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1324" s="4"/>
     </row>
-    <row r="1325" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1325" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1325" s="4"/>
     </row>
-    <row r="1326" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1326" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1326" s="4"/>
     </row>
-    <row r="1327" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1327" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1327" s="4"/>
     </row>
-    <row r="1328" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1328" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1328" s="4"/>
     </row>
-    <row r="1329" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1329" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1329" s="4"/>
     </row>
-    <row r="1330" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1330" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1330" s="4"/>
     </row>
-    <row r="1331" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1331" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1331" s="4"/>
     </row>
-    <row r="1332" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1332" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1332" s="4"/>
     </row>
-    <row r="1333" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1333" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1333" s="4"/>
     </row>
-    <row r="1334" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1334" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1334" s="4"/>
     </row>
-    <row r="1335" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1335" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1335" s="4"/>
     </row>
-    <row r="1336" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1336" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1336" s="4"/>
     </row>
-    <row r="1337" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1337" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1337" s="4"/>
     </row>
-    <row r="1338" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1338" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1338" s="4"/>
     </row>
-    <row r="1339" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1339" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1339" s="4"/>
     </row>
-    <row r="1340" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1340" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1340" s="4"/>
     </row>
-    <row r="1341" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1341" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1341" s="4"/>
     </row>
-    <row r="1342" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1342" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1342" s="4"/>
     </row>
-    <row r="1343" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1343" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1343" s="4"/>
     </row>
-    <row r="1344" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1344" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1344" s="4"/>
     </row>
-    <row r="1345" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1345" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1345" s="4"/>
     </row>
-    <row r="1346" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1346" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1346" s="4"/>
     </row>
-    <row r="1347" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1347" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1347" s="4"/>
     </row>
-    <row r="1348" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1348" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1348" s="4"/>
     </row>
-    <row r="1349" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1349" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1349" s="4"/>
     </row>
-    <row r="1350" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1350" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1350" s="4"/>
     </row>
-    <row r="1351" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1351" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1351" s="4"/>
     </row>
-    <row r="1352" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1352" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1352" s="4"/>
     </row>
-    <row r="1353" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1353" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1353" s="4"/>
     </row>
-    <row r="1354" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1354" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1354" s="4"/>
     </row>
-    <row r="1355" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1355" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1355" s="4"/>
     </row>
-    <row r="1356" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1356" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1356" s="4"/>
     </row>
-    <row r="1357" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1357" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1357" s="4"/>
     </row>
-    <row r="1358" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1358" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1358" s="4"/>
     </row>
-    <row r="1359" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1359" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1359" s="4"/>
     </row>
-    <row r="1360" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1360" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1360" s="4"/>
     </row>
-    <row r="1361" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1361" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1361" s="4"/>
     </row>
-    <row r="1362" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1362" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1362" s="4"/>
     </row>
-    <row r="1363" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1363" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1363" s="4"/>
     </row>
-    <row r="1364" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1364" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1364" s="4"/>
     </row>
-    <row r="1365" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1365" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1365" s="4"/>
     </row>
-    <row r="1366" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1366" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1366" s="4"/>
     </row>
-    <row r="1367" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1367" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1367" s="4"/>
     </row>
-    <row r="1368" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1368" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1368" s="4"/>
     </row>
-    <row r="1369" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1369" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1369" s="4"/>
     </row>
-    <row r="1370" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1370" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1370" s="4"/>
     </row>
-    <row r="1371" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1371" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1371" s="4"/>
     </row>
-    <row r="1372" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1372" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1372" s="4"/>
     </row>
-    <row r="1373" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1373" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1373" s="4"/>
     </row>
-    <row r="1374" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1374" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1374" s="4"/>
     </row>
-    <row r="1375" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1375" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1375" s="4"/>
     </row>
-    <row r="1376" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1376" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1376" s="4"/>
     </row>
-    <row r="1377" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1377" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1377" s="4"/>
     </row>
-    <row r="1378" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1378" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1378" s="4"/>
     </row>
-    <row r="1379" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1379" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1379" s="4"/>
     </row>
-    <row r="1380" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1380" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1380" s="4"/>
     </row>
-    <row r="1381" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1381" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1381" s="4"/>
     </row>
-    <row r="1382" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1382" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1382" s="4"/>
     </row>
-    <row r="1383" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1383" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1383" s="4"/>
     </row>
-    <row r="1384" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1384" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1384" s="4"/>
     </row>
-    <row r="1385" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1385" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1385" s="4"/>
     </row>
-    <row r="1386" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1386" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1386" s="4"/>
     </row>
-    <row r="1387" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1387" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1387" s="4"/>
     </row>
-    <row r="1388" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1388" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1388" s="4"/>
     </row>
-    <row r="1389" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1389" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1389" s="4"/>
     </row>
-    <row r="1390" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1390" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1390" s="4"/>
     </row>
-    <row r="1391" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1391" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1391" s="4"/>
     </row>
-    <row r="1392" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1392" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1392" s="4"/>
     </row>
-    <row r="1393" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1393" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1393" s="4"/>
     </row>
-    <row r="1394" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1394" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1394" s="4"/>
     </row>
-    <row r="1395" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1395" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1395" s="4"/>
     </row>
-    <row r="1396" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1396" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1396" s="4"/>
     </row>
-    <row r="1397" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1397" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1397" s="4"/>
     </row>
-    <row r="1398" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1398" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1398" s="4"/>
     </row>
-    <row r="1399" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1399" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1399" s="4"/>
     </row>
-    <row r="1400" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1400" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1400" s="4"/>
     </row>
-    <row r="1401" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1401" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1401" s="4"/>
     </row>
-    <row r="1402" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1402" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1402" s="4"/>
     </row>
-    <row r="1403" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1403" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1403" s="4"/>
     </row>
-    <row r="1404" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1404" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1404" s="4"/>
     </row>
-    <row r="1405" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1405" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1405" s="4"/>
     </row>
-    <row r="1406" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1406" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1406" s="4"/>
     </row>
-    <row r="1407" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1407" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1407" s="4"/>
     </row>
-    <row r="1408" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1408" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1408" s="4"/>
     </row>
-    <row r="1409" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1409" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1409" s="4"/>
     </row>
-    <row r="1410" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1410" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1410" s="4"/>
     </row>
-    <row r="1411" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1411" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1411" s="4"/>
     </row>
-    <row r="1412" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1412" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1412" s="4"/>
     </row>
-    <row r="1413" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1413" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1413" s="4"/>
     </row>
-    <row r="1414" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1414" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1414" s="4"/>
     </row>
-    <row r="1415" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1415" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1415" s="4"/>
     </row>
-    <row r="1416" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1416" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1416" s="4"/>
     </row>
-    <row r="1417" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1417" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1417" s="4"/>
     </row>
-    <row r="1418" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1418" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1418" s="4"/>
     </row>
-    <row r="1419" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1419" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1419" s="4"/>
     </row>
-    <row r="1420" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1420" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1420" s="4"/>
     </row>
-    <row r="1421" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1421" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1421" s="4"/>
     </row>
-    <row r="1422" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1422" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1422" s="4"/>
     </row>
-    <row r="1423" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1423" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1423" s="4"/>
     </row>
-    <row r="1424" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1424" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1424" s="4"/>
     </row>
-    <row r="1425" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1425" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1425" s="4"/>
     </row>
-    <row r="1426" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1426" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1426" s="4"/>
     </row>
-    <row r="1427" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1427" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1427" s="4"/>
     </row>
-    <row r="1428" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1428" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1428" s="4"/>
     </row>
-    <row r="1429" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1429" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1429" s="4"/>
     </row>
-    <row r="1430" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1430" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1430" s="4"/>
     </row>
-    <row r="1431" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1431" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1431" s="4"/>
     </row>
-    <row r="1432" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1432" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1432" s="4"/>
     </row>
-    <row r="1433" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1433" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1433" s="4"/>
     </row>
-    <row r="1434" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1434" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1434" s="4"/>
     </row>
-    <row r="1435" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1435" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1435" s="4"/>
     </row>
-    <row r="1436" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1436" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1436" s="4"/>
     </row>
-    <row r="1437" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1437" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1437" s="4"/>
     </row>
-    <row r="1438" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1438" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1438" s="4"/>
     </row>
-    <row r="1439" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1439" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1439" s="4"/>
     </row>
-    <row r="1440" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1440" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1440" s="4"/>
     </row>
-    <row r="1441" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1441" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1441" s="4"/>
     </row>
-    <row r="1442" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1442" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1442" s="4"/>
     </row>
-    <row r="1443" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1443" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1443" s="4"/>
     </row>
-    <row r="1444" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1444" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1444" s="4"/>
     </row>
-    <row r="1445" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1445" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1445" s="4"/>
     </row>
-    <row r="1446" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1446" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1446" s="4"/>
     </row>
-    <row r="1447" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1447" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1447" s="4"/>
     </row>
-    <row r="1448" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1448" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1448" s="4"/>
     </row>
-    <row r="1449" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1449" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1449" s="4"/>
     </row>
-    <row r="1450" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1450" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1450" s="4"/>
     </row>
-    <row r="1451" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1451" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1451" s="4"/>
     </row>
-    <row r="1452" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1452" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1452" s="4"/>
     </row>
-    <row r="1453" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1453" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1453" s="4"/>
     </row>
-    <row r="1454" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1454" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1454" s="4"/>
     </row>
-    <row r="1455" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1455" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1455" s="4"/>
     </row>
-    <row r="1456" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1456" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1456" s="4"/>
     </row>
-    <row r="1457" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1457" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1457" s="4"/>
     </row>
-    <row r="1458" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1458" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1458" s="4"/>
     </row>
-    <row r="1459" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1459" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1459" s="4"/>
     </row>
-    <row r="1460" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1460" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1460" s="4"/>
     </row>
-    <row r="1461" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1461" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1461" s="4"/>
     </row>
-    <row r="1462" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1462" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1462" s="4"/>
     </row>
-    <row r="1463" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1463" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1463" s="4"/>
     </row>
-    <row r="1464" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1464" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1464" s="4"/>
     </row>
-    <row r="1465" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1465" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1465" s="4"/>
     </row>
-    <row r="1466" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1466" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1466" s="4"/>
     </row>
-    <row r="1467" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1467" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1467" s="4"/>
     </row>
-    <row r="1468" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1468" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1468" s="4"/>
     </row>
-    <row r="1469" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1469" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1469" s="4"/>
     </row>
-    <row r="1470" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1470" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1470" s="4"/>
     </row>
-    <row r="1471" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1471" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1471" s="4"/>
     </row>
-    <row r="1472" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1472" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1472" s="4"/>
     </row>
-    <row r="1473" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1473" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1473" s="4"/>
     </row>
-    <row r="1474" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1474" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1474" s="4"/>
     </row>
-    <row r="1475" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1475" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1475" s="4"/>
     </row>
-    <row r="1476" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1476" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1476" s="4"/>
     </row>
-    <row r="1477" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1477" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1477" s="4"/>
     </row>
-    <row r="1478" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1478" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1478" s="4"/>
     </row>
-    <row r="1479" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1479" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1479" s="4"/>
     </row>
-    <row r="1480" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1480" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1480" s="4"/>
     </row>
-    <row r="1481" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1481" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1481" s="4"/>
     </row>
-    <row r="1482" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1482" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1482" s="4"/>
     </row>
-    <row r="1483" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1483" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1483" s="4"/>
     </row>
-    <row r="1484" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1484" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1484" s="4"/>
     </row>
-    <row r="1485" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1485" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1485" s="4"/>
     </row>
-    <row r="1486" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1486" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1486" s="4"/>
     </row>
-    <row r="1487" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1487" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1487" s="4"/>
     </row>
-    <row r="1488" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1488" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1488" s="4"/>
     </row>
-    <row r="1489" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1489" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1489" s="4"/>
     </row>
-    <row r="1490" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1490" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1490" s="4"/>
     </row>
-    <row r="1491" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1491" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1491" s="4"/>
     </row>
-    <row r="1492" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1492" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1492" s="4"/>
     </row>
-    <row r="1493" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1493" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1493" s="4"/>
     </row>
-    <row r="1494" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1494" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1494" s="4"/>
     </row>
-    <row r="1495" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1495" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1495" s="4"/>
     </row>
-    <row r="1496" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1496" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1496" s="4"/>
     </row>
-    <row r="1497" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1497" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1497" s="4"/>
     </row>
-    <row r="1498" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1498" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1498" s="4"/>
     </row>
-    <row r="1499" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1499" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1499" s="4"/>
     </row>
-    <row r="1500" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1500" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1500" s="4"/>
     </row>
-    <row r="1501" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1501" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1501" s="4"/>
     </row>
-    <row r="1502" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1502" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1502" s="4"/>
     </row>
-    <row r="1503" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1503" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1503" s="4"/>
     </row>
-    <row r="1504" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1504" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1504" s="4"/>
     </row>
-    <row r="1505" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1505" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1505" s="4"/>
     </row>
-    <row r="1506" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1506" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1506" s="4"/>
     </row>
-    <row r="1507" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1507" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1507" s="4"/>
     </row>
-    <row r="1508" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1508" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1508" s="4"/>
     </row>
-    <row r="1509" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1509" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1509" s="4"/>
     </row>
-    <row r="1510" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1510" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1510" s="4"/>
     </row>
-    <row r="1511" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1511" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1511" s="4"/>
     </row>
-    <row r="1512" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1512" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1512" s="4"/>
     </row>
-    <row r="1513" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1513" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1513" s="4"/>
     </row>
-    <row r="1514" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1514" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1514" s="4"/>
     </row>
-    <row r="1515" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1515" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1515" s="4"/>
     </row>
-    <row r="1516" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1516" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1516" s="4"/>
     </row>
-    <row r="1517" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1517" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1517" s="4"/>
     </row>
-    <row r="1518" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1518" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1518" s="4"/>
     </row>
-    <row r="1519" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1519" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1519" s="4"/>
     </row>
-    <row r="1520" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1520" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1520" s="4"/>
     </row>
-    <row r="1521" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1521" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1521" s="4"/>
     </row>
-    <row r="1522" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1522" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1522" s="4"/>
     </row>
-    <row r="1523" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1523" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1523" s="4"/>
     </row>
-    <row r="1524" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1524" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1524" s="4"/>
     </row>
-    <row r="1525" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1525" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1525" s="4"/>
     </row>
-    <row r="1526" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1526" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1526" s="4"/>
     </row>
-    <row r="1527" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1527" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1527" s="4"/>
     </row>
-    <row r="1528" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1528" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1528" s="4"/>
     </row>
-    <row r="1529" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1529" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1529" s="4"/>
     </row>
-    <row r="1530" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1530" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1530" s="4"/>
     </row>
-    <row r="1531" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1531" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1531" s="4"/>
     </row>
-    <row r="1532" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1532" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1532" s="4"/>
     </row>
-    <row r="1533" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1533" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1533" s="4"/>
     </row>
-    <row r="1534" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1534" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1534" s="4"/>
     </row>
-    <row r="1535" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1535" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1535" s="4"/>
     </row>
-    <row r="1536" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1536" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1536" s="4"/>
     </row>
-    <row r="1537" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1537" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1537" s="4"/>
     </row>
-    <row r="1538" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1538" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1538" s="4"/>
     </row>
-    <row r="1539" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1539" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1539" s="4"/>
     </row>
-    <row r="1540" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1540" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1540" s="4"/>
     </row>
-    <row r="1541" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1541" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1541" s="4"/>
     </row>
-    <row r="1542" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1542" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1542" s="4"/>
     </row>
-    <row r="1543" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1543" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1543" s="4"/>
     </row>
-    <row r="1544" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1544" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1544" s="4"/>
     </row>
-    <row r="1545" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1545" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1545" s="4"/>
     </row>
-    <row r="1546" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1546" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1546" s="4"/>
     </row>
-    <row r="1547" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1547" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1547" s="4"/>
     </row>
-    <row r="1548" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1548" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1548" s="4"/>
     </row>
-    <row r="1549" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1549" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1549" s="4"/>
     </row>
-    <row r="1550" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1550" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1550" s="4"/>
     </row>
-    <row r="1551" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1551" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1551" s="4"/>
     </row>
-    <row r="1552" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1552" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1552" s="4"/>
     </row>
-    <row r="1553" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1553" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1553" s="4"/>
     </row>
-    <row r="1554" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1554" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1554" s="4"/>
     </row>
-    <row r="1555" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1555" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1555" s="4"/>
     </row>
-    <row r="1556" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1556" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1556" s="4"/>
     </row>
-    <row r="1557" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1557" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1557" s="4"/>
     </row>
-    <row r="1558" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1558" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1558" s="4"/>
     </row>
-    <row r="1559" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1559" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1559" s="4"/>
     </row>
-    <row r="1560" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1560" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1560" s="4"/>
     </row>
-    <row r="1561" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1561" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1561" s="4"/>
     </row>
-    <row r="1562" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1562" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1562" s="4"/>
     </row>
-    <row r="1563" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1563" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1563" s="4"/>
     </row>
-    <row r="1564" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1564" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1564" s="4"/>
     </row>
-    <row r="1565" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1565" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1565" s="4"/>
     </row>
-    <row r="1566" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1566" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1566" s="4"/>
     </row>
-    <row r="1567" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1567" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1567" s="4"/>
     </row>
-    <row r="1568" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1568" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1568" s="4"/>
     </row>
-    <row r="1569" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1569" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1569" s="4"/>
     </row>
-    <row r="1570" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1570" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1570" s="4"/>
     </row>
-    <row r="1571" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1571" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1571" s="4"/>
     </row>
-    <row r="1572" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1572" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1572" s="4"/>
     </row>
-    <row r="1573" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1573" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1573" s="4"/>
     </row>
-    <row r="1574" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1574" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1574" s="4"/>
     </row>
-    <row r="1575" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1575" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1575" s="4"/>
     </row>
-    <row r="1576" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1576" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1576" s="4"/>
     </row>
-    <row r="1577" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1577" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1577" s="4"/>
     </row>
-    <row r="1578" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1578" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1578" s="4"/>
     </row>
-    <row r="1579" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1579" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1579" s="4"/>
     </row>
-    <row r="1580" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1580" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1580" s="4"/>
     </row>
-    <row r="1581" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1581" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1581" s="4"/>
     </row>
-    <row r="1582" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1582" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1582" s="4"/>
     </row>
-    <row r="1583" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1583" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1583" s="4"/>
     </row>
-    <row r="1584" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1584" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1584" s="4"/>
     </row>
-    <row r="1585" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1585" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1585" s="4"/>
     </row>
-    <row r="1586" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1586" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1586" s="4"/>
     </row>
-    <row r="1587" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1587" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1587" s="4"/>
     </row>
-    <row r="1588" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1588" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1588" s="4"/>
     </row>
-    <row r="1589" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1589" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1589" s="4"/>
     </row>
-    <row r="1590" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1590" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1590" s="4"/>
     </row>
-    <row r="1591" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1591" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1591" s="4"/>
     </row>
-    <row r="1592" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1592" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1592" s="4"/>
     </row>
-    <row r="1593" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1593" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1593" s="4"/>
     </row>
-    <row r="1594" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1594" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1594" s="4"/>
     </row>
-    <row r="1595" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1595" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1595" s="4"/>
     </row>
-    <row r="1596" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1596" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1596" s="4"/>
     </row>
-    <row r="1597" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1597" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1597" s="4"/>
     </row>
-    <row r="1598" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1598" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1598" s="4"/>
     </row>
-    <row r="1599" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1599" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1599" s="4"/>
     </row>
-    <row r="1600" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1600" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1600" s="4"/>
     </row>
-    <row r="1601" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1601" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1601" s="4"/>
     </row>
-    <row r="1602" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1602" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1602" s="4"/>
     </row>
-    <row r="1603" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1603" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1603" s="4"/>
     </row>
-    <row r="1604" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1604" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1604" s="4"/>
     </row>
-    <row r="1605" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1605" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1605" s="4"/>
     </row>
-    <row r="1606" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1606" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1606" s="4"/>
     </row>
-    <row r="1607" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1607" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1607" s="4"/>
     </row>
-    <row r="1608" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1608" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1608" s="4"/>
     </row>
-    <row r="1609" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1609" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1609" s="4"/>
     </row>
-    <row r="1610" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1610" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1610" s="4"/>
     </row>
-    <row r="1611" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1611" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1611" s="4"/>
     </row>
-    <row r="1612" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1612" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1612" s="4"/>
     </row>
-    <row r="1613" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1613" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1613" s="4"/>
     </row>
-    <row r="1614" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1614" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1614" s="4"/>
     </row>
-    <row r="1615" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1615" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1615" s="4"/>
     </row>
-    <row r="1616" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1616" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1616" s="4"/>
     </row>
-    <row r="1617" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1617" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1617" s="4"/>
     </row>
-    <row r="1618" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1618" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1618" s="4"/>
     </row>
-    <row r="1619" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1619" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1619" s="4"/>
     </row>
-    <row r="1620" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1620" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1620" s="4"/>
     </row>
-    <row r="1621" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1621" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1621" s="4"/>
     </row>
-    <row r="1622" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1622" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1622" s="4"/>
     </row>
-    <row r="1623" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1623" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1623" s="4"/>
     </row>
-    <row r="1624" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1624" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1624" s="4"/>
     </row>
-    <row r="1625" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1625" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1625" s="4"/>
     </row>
-    <row r="1626" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1626" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1626" s="4"/>
     </row>
-    <row r="1627" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1627" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1627" s="4"/>
     </row>
-    <row r="1628" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1628" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1628" s="4"/>
     </row>
-    <row r="1629" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1629" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1629" s="4"/>
     </row>
-    <row r="1630" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1630" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1630" s="4"/>
     </row>
-    <row r="1631" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1631" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1631" s="4"/>
     </row>
-    <row r="1632" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1632" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1632" s="4"/>
     </row>
-    <row r="1633" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1633" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1633" s="4"/>
     </row>
-    <row r="1634" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1634" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1634" s="4"/>
     </row>
-    <row r="1635" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1635" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1635" s="4"/>
     </row>
-    <row r="1636" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1636" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1636" s="4"/>
     </row>
-    <row r="1637" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1637" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1637" s="4"/>
     </row>
-    <row r="1638" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1638" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1638" s="4"/>
     </row>
-    <row r="1639" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1639" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1639" s="4"/>
     </row>
-    <row r="1640" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1640" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1640" s="4"/>
     </row>
-    <row r="1641" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1641" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1641" s="4"/>
     </row>
-    <row r="1642" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1642" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1642" s="4"/>
     </row>
-    <row r="1643" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1643" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1643" s="4"/>
     </row>
-    <row r="1644" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1644" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1644" s="4"/>
     </row>
-    <row r="1645" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1645" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1645" s="4"/>
     </row>
-    <row r="1646" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1646" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1646" s="4"/>
     </row>
-    <row r="1647" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1647" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1647" s="4"/>
     </row>
-    <row r="1648" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1648" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1648" s="4"/>
     </row>
-    <row r="1649" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1649" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1649" s="4"/>
     </row>
-    <row r="1650" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1650" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1650" s="4"/>
     </row>
-    <row r="1651" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1651" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1651" s="4"/>
     </row>
-    <row r="1652" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1652" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1652" s="4"/>
     </row>
-    <row r="1653" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1653" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1653" s="4"/>
     </row>
-    <row r="1654" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1654" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1654" s="4"/>
     </row>
-    <row r="1655" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1655" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1655" s="4"/>
     </row>
-    <row r="1656" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1656" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1656" s="4"/>
     </row>
-    <row r="1657" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1657" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1657" s="4"/>
     </row>
-    <row r="1658" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1658" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1658" s="4"/>
     </row>
-    <row r="1659" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1659" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1659" s="4"/>
     </row>
-    <row r="1660" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1660" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1660" s="4"/>
     </row>
-    <row r="1661" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1661" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1661" s="4"/>
     </row>
-    <row r="1662" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1662" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1662" s="4"/>
     </row>
-    <row r="1663" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1663" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1663" s="4"/>
     </row>
-    <row r="1664" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1664" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1664" s="4"/>
     </row>
-    <row r="1665" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1665" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1665" s="4"/>
     </row>
-    <row r="1666" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1666" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1666" s="4"/>
     </row>
-    <row r="1667" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1667" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1667" s="4"/>
     </row>
-    <row r="1668" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1668" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1668" s="4"/>
     </row>
-    <row r="1669" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1669" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1669" s="4"/>
     </row>
-    <row r="1670" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1670" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1670" s="4"/>
     </row>
-    <row r="1671" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1671" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1671" s="4"/>
     </row>
-    <row r="1672" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1672" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1672" s="4"/>
     </row>
-    <row r="1673" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1673" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1673" s="4"/>
     </row>
-    <row r="1674" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1674" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1674" s="4"/>
     </row>
-    <row r="1675" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1675" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1675" s="4"/>
     </row>
-    <row r="1676" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1676" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1676" s="4"/>
     </row>
-    <row r="1677" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1677" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1677" s="4"/>
     </row>
-    <row r="1678" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1678" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1678" s="4"/>
     </row>
-    <row r="1679" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1679" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1679" s="4"/>
     </row>
-    <row r="1680" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1680" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1680" s="4"/>
     </row>
-    <row r="1681" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1681" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1681" s="4"/>
     </row>
-    <row r="1682" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1682" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1682" s="4"/>
     </row>
-    <row r="1683" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1683" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1683" s="4"/>
     </row>
-    <row r="1684" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1684" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1684" s="4"/>
     </row>
-    <row r="1685" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1685" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1685" s="4"/>
     </row>
-    <row r="1686" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1686" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1686" s="4"/>
     </row>
-    <row r="1687" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1687" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1687" s="4"/>
     </row>
-    <row r="1688" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1688" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1688" s="4"/>
     </row>
-    <row r="1689" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1689" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1689" s="4"/>
     </row>
-    <row r="1690" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1690" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1690" s="4"/>
     </row>
-    <row r="1691" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1691" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1691" s="4"/>
     </row>
-    <row r="1692" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1692" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1692" s="4"/>
     </row>
-    <row r="1693" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1693" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1693" s="4"/>
     </row>
-    <row r="1694" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1694" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1694" s="4"/>
     </row>
-    <row r="1695" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1695" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1695" s="4"/>
     </row>
-    <row r="1696" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1696" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1696" s="4"/>
     </row>
-    <row r="1697" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1697" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1697" s="4"/>
     </row>
-    <row r="1698" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1698" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1698" s="4"/>
     </row>
-    <row r="1699" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1699" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1699" s="4"/>
     </row>
-    <row r="1700" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1700" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1700" s="4"/>
     </row>
-    <row r="1701" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1701" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1701" s="4"/>
     </row>
-    <row r="1702" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1702" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1702" s="4"/>
     </row>
-    <row r="1703" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1703" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1703" s="4"/>
     </row>
-    <row r="1704" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1704" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1704" s="4"/>
     </row>
-    <row r="1705" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1705" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1705" s="4"/>
     </row>
-    <row r="1706" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1706" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1706" s="4"/>
     </row>
-    <row r="1707" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1707" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1707" s="4"/>
     </row>
-    <row r="1708" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1708" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1708" s="4"/>
     </row>
-    <row r="1709" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1709" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1709" s="4"/>
     </row>
-    <row r="1710" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1710" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1710" s="4"/>
     </row>
-    <row r="1711" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1711" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1711" s="4"/>
     </row>
-    <row r="1712" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1712" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1712" s="4"/>
     </row>
-    <row r="1713" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1713" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1713" s="4"/>
     </row>
-    <row r="1714" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1714" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1714" s="4"/>
     </row>
-    <row r="1715" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1715" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1715" s="4"/>
     </row>
-    <row r="1716" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1716" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1716" s="4"/>
     </row>
-    <row r="1717" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1717" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1717" s="4"/>
     </row>
-    <row r="1718" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1718" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1718" s="4"/>
     </row>
-    <row r="1719" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1719" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1719" s="4"/>
     </row>
-    <row r="1720" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1720" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1720" s="4"/>
     </row>
-    <row r="1721" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1721" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1721" s="4"/>
     </row>
-    <row r="1722" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1722" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1722" s="4"/>
     </row>
-    <row r="1723" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1723" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1723" s="4"/>
     </row>
-    <row r="1724" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1724" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1724" s="4"/>
     </row>
-    <row r="1725" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1725" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1725" s="4"/>
     </row>
-    <row r="1726" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1726" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1726" s="4"/>
     </row>
-    <row r="1727" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1727" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1727" s="4"/>
     </row>
-    <row r="1728" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1728" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1728" s="4"/>
     </row>
-    <row r="1729" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1729" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1729" s="4"/>
     </row>
-    <row r="1730" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1730" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1730" s="4"/>
     </row>
-    <row r="1731" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1731" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1731" s="4"/>
     </row>
-    <row r="1732" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1732" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1732" s="4"/>
     </row>
-    <row r="1733" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1733" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1733" s="4"/>
     </row>
-    <row r="1734" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1734" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1734" s="4"/>
     </row>
-    <row r="1735" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1735" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1735" s="4"/>
     </row>
-    <row r="1736" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1736" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1736" s="4"/>
     </row>
-    <row r="1737" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1737" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1737" s="4"/>
     </row>
-    <row r="1738" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1738" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1738" s="4"/>
     </row>
-    <row r="1739" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1739" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1739" s="4"/>
     </row>
-    <row r="1740" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1740" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1740" s="4"/>
     </row>
-    <row r="1741" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1741" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1741" s="4"/>
     </row>
-    <row r="1742" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1742" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1742" s="4"/>
     </row>
-    <row r="1743" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1743" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1743" s="4"/>
     </row>
-    <row r="1744" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1744" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1744" s="4"/>
     </row>
-    <row r="1745" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1745" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1745" s="4"/>
     </row>
-    <row r="1746" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1746" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1746" s="4"/>
     </row>
-    <row r="1747" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1747" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1747" s="4"/>
     </row>
-    <row r="1748" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1748" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1748" s="4"/>
     </row>
-    <row r="1749" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1749" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1749" s="4"/>
     </row>
-    <row r="1750" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1750" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1750" s="4"/>
     </row>
-    <row r="1751" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1751" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1751" s="4"/>
     </row>
-    <row r="1752" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1752" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1752" s="4"/>
     </row>
-    <row r="1753" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1753" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1753" s="4"/>
     </row>
-    <row r="1754" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1754" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1754" s="4"/>
     </row>
-    <row r="1755" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1755" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1755" s="4"/>
     </row>
-    <row r="1756" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1756" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1756" s="4"/>
     </row>
-    <row r="1757" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1757" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1757" s="4"/>
     </row>
-    <row r="1758" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1758" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1758" s="4"/>
     </row>
-    <row r="1759" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1759" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1759" s="4"/>
     </row>
-    <row r="1760" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1760" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1760" s="4"/>
     </row>
-    <row r="1761" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1761" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1761" s="4"/>
     </row>
-    <row r="1762" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1762" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1762" s="4"/>
     </row>
-    <row r="1763" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1763" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1763" s="4"/>
     </row>
-    <row r="1764" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1764" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1764" s="4"/>
     </row>
-    <row r="1765" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1765" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1765" s="4"/>
     </row>
-    <row r="1766" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1766" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1766" s="4"/>
     </row>
-    <row r="1767" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1767" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1767" s="4"/>
     </row>
-    <row r="1768" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1768" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1768" s="4"/>
     </row>
-    <row r="1769" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1769" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1769" s="4"/>
     </row>
-    <row r="1770" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1770" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1770" s="4"/>
     </row>
-    <row r="1771" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1771" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1771" s="4"/>
     </row>
-    <row r="1772" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1772" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1772" s="4"/>
     </row>
-    <row r="1773" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1773" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1773" s="4"/>
     </row>
-    <row r="1774" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1774" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1774" s="4"/>
     </row>
-    <row r="1775" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="1775" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C1775" s="4"/>
     </row>
   </sheetData>
